--- a/wiwynn/dist/20261025_緯穎模型_v0.1.1.xlsx
+++ b/wiwynn/dist/20261025_緯穎模型_v0.1.1.xlsx
@@ -5663,7 +5663,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.3.xlsx</t>
+      <t xml:space="preserve">_v0.3.1.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -5862,7 +5862,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.3.xlsx</t>
+      <t xml:space="preserve">_v0.3.1.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -5983,7 +5983,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.3.xlsx</t>
+      <t xml:space="preserve">_v0.3.1.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -6104,7 +6104,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.3.xlsx</t>
+      <t xml:space="preserve">_v0.3.1.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -6225,7 +6225,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.3.xlsx</t>
+      <t xml:space="preserve">_v0.3.1.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -6346,7 +6346,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.3.xlsx</t>
+      <t xml:space="preserve">_v0.3.1.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -6578,7 +6578,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.3.xlsx</t>
+      <t xml:space="preserve">_v0.3.1.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -34660,7 +34660,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.3.xlsx</t>
+      <t xml:space="preserve">_v0.3.1.xlsx</t>
     </r>
     <r>
       <rPr>

--- a/wiwynn/dist/20261025_緯穎模型_v0.1.1.xlsx
+++ b/wiwynn/dist/20261025_緯穎模型_v0.1.1.xlsx
@@ -4589,7 +4589,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">markets/network/dist/20261023_AI</t>
+      <t xml:space="preserve">markets/network/dist/20261026_AI</t>
     </r>
     <r>
       <rPr>
@@ -4608,7 +4608,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.2.2.xlsx</t>
+      <t xml:space="preserve">_v0.2.3.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -34565,7 +34565,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">markets/network/dist/20261023_AI</t>
+      <t xml:space="preserve">markets/network/dist/20261026_AI</t>
     </r>
     <r>
       <rPr>
@@ -34584,7 +34584,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.2.2.xlsx</t>
+      <t xml:space="preserve">_v0.2.3.xlsx</t>
     </r>
     <r>
       <rPr>

--- a/wiwynn/dist/20261025_緯穎模型_v0.1.1.xlsx
+++ b/wiwynn/dist/20261025_緯穎模型_v0.1.1.xlsx
@@ -4902,7 +4902,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">markets/chip_bridge/dist/20261023_</t>
+      <t xml:space="preserve">markets/chip_bridge/dist/20261027_</t>
     </r>
     <r>
       <rPr>
@@ -4921,6 +4921,328 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
+      <t xml:space="preserve">_v0.2.2.xlsx</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">｜</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">In!E10</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">GB300</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">）、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">H10</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">VR200</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Tokenomics v20.1 IF_CapexIT</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">（經橋接表；唯讀）</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">itpg_vr</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">每 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">GW IT </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">資本支出（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">VR200</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">；</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2027 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">起）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">同上；</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">ASIC </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">機架未另訂（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Assumed</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">：同 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">VR200</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">）</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">vr26</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2026 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">年部署中 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Rubin </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">世代占比（混合用）</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">%</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">quanta/dist/20261025_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">廣達模型</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
       <t xml:space="preserve">_v0.2.1.xlsx</t>
     </r>
     <r>
@@ -4940,16 +5262,89 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">In!E10</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">（</t>
+      <t xml:space="preserve">In!D11:F11</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">廣達模型輸入（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">TrendForce 2026 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">組合 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Rubin 22%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">）</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">racks_gb</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">每 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">GW </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">機架數（</t>
     </r>
     <r>
       <rPr>
@@ -4968,405 +5363,10 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">）、</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">H10</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">（</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">VR200</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
       <t xml:space="preserve">）</t>
     </r>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Tokenomics v20.1 IF_CapexIT</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">（經橋接表；唯讀）</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">itpg_vr</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">每 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">GW IT </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">資本支出（</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">VR200</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">；</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">2027 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">起）</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">同上；</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">ASIC </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">機架未另訂（</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Assumed</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">：同 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">VR200</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">）</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">vr26</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">2026 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">年部署中 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Rubin </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">世代占比（混合用）</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">%</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">quanta/dist/20261025_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">廣達模型</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">_v0.2.1.xlsx</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">｜</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">In!D11:F11</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">廣達模型輸入（</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">TrendForce 2026 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">組合 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Rubin 22%</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">）</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">racks_gb</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">每 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">GW </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">機架數（</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">GB300</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">）</t>
-    </r>
-  </si>
-  <si>
     <t xml:space="preserve">架</t>
   </si>
   <si>
@@ -5378,7 +5378,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">markets/chip_bridge/dist/20261023_</t>
+      <t xml:space="preserve">markets/chip_bridge/dist/20261027_</t>
     </r>
     <r>
       <rPr>
@@ -5397,7 +5397,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.2.1.xlsx</t>
+      <t xml:space="preserve">_v0.2.2.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -34603,7 +34603,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">markets/chip_bridge/dist/20261023_</t>
+      <t xml:space="preserve">markets/chip_bridge/dist/20261027_</t>
     </r>
     <r>
       <rPr>
@@ -34622,7 +34622,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.2.1.xlsx</t>
+      <t xml:space="preserve">_v0.2.2.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -35601,7 +35601,7 @@
         <v>30</v>
       </c>
       <c r="E5" s="7" t="n">
-        <v>781.872916666667</v>
+        <v>781.872916666666</v>
       </c>
       <c r="G5" s="8" t="s">
         <v>31</v>
@@ -37817,7 +37817,7 @@
       <c r="D98" s="9"/>
       <c r="E98" s="13" t="n">
         <f aca="false">(PL!G26+nim10)/2</f>
-        <v>0.0488998284347512</v>
+        <v>0.0488998284347513</v>
       </c>
       <c r="F98" s="9"/>
       <c r="G98" s="9" t="s">
@@ -38497,7 +38497,7 @@
       </c>
       <c r="C5" s="22" t="n">
         <f aca="false">PL!D67</f>
-        <v>634.616531285011</v>
+        <v>634.61653128501</v>
       </c>
       <c r="D5" s="22" t="n">
         <f aca="false">PL!E67</f>
@@ -38609,15 +38609,15 @@
       </c>
       <c r="D9" s="17" t="n">
         <f aca="false">PL!E72</f>
-        <v>0.0498832807117864</v>
+        <v>0.0498832807117865</v>
       </c>
       <c r="E9" s="17" t="n">
         <f aca="false">PL!F72</f>
-        <v>0.0509096185694461</v>
+        <v>0.0509096185694462</v>
       </c>
       <c r="F9" s="17" t="n">
         <f aca="false">PL!G72</f>
-        <v>0.0488501692055052</v>
+        <v>0.0488501692055053</v>
       </c>
       <c r="G9" s="8" t="s">
         <v>402</v>
@@ -38640,7 +38640,7 @@
         <v>0.127201317776965</v>
       </c>
       <c r="F10" s="24" t="n">
-        <v>0.120506511578177</v>
+        <v>0.120506511578178</v>
       </c>
       <c r="G10" s="8" t="s">
         <v>404</v>
@@ -38663,11 +38663,11 @@
       </c>
       <c r="E11" s="22" t="n">
         <f aca="false">PL!F73/fx</f>
-        <v>73.5093030013044</v>
+        <v>73.5093030013045</v>
       </c>
       <c r="F11" s="22" t="n">
         <f aca="false">PL!G73/fx</f>
-        <v>80.3512312305394</v>
+        <v>80.3512312305395</v>
       </c>
       <c r="G11" s="4" t="s">
         <v>406</v>
@@ -38713,11 +38713,11 @@
       </c>
       <c r="D13" s="22" t="n">
         <f aca="false">PL!E75/fx</f>
-        <v>53.9800278219409</v>
+        <v>53.980027821941</v>
       </c>
       <c r="E13" s="22" t="n">
         <f aca="false">PL!F75/fx</f>
-        <v>66.158372701174</v>
+        <v>66.1583727011741</v>
       </c>
       <c r="F13" s="22" t="n">
         <f aca="false">PL!G75/fx</f>
@@ -38733,7 +38733,7 @@
       </c>
       <c r="C14" s="23" t="n">
         <f aca="false">PL!D81</f>
-        <v>0.935061049524468</v>
+        <v>0.935061049524469</v>
       </c>
       <c r="D14" s="23" t="n">
         <f aca="false">PL!E81</f>
@@ -38892,7 +38892,7 @@
       </c>
       <c r="J5" s="25" t="n">
         <f aca="false">J78</f>
-        <v>3513.54543594395</v>
+        <v>3513.54543594396</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -38908,7 +38908,7 @@
       </c>
       <c r="E6" s="18" t="n">
         <f aca="false">E79</f>
-        <v>0.730205547569951</v>
+        <v>0.730205547569952</v>
       </c>
       <c r="F6" s="18" t="n">
         <f aca="false">F79</f>
@@ -38916,15 +38916,15 @@
       </c>
       <c r="G6" s="18" t="n">
         <f aca="false">G79</f>
-        <v>0.0316931767891091</v>
+        <v>0.0316931767891089</v>
       </c>
       <c r="H6" s="26" t="n">
         <f aca="false">H79</f>
-        <v>0.0411287845260727</v>
+        <v>0.0411287845260726</v>
       </c>
       <c r="I6" s="26" t="n">
         <f aca="false">I79</f>
-        <v>0.0505643922630364</v>
+        <v>0.0505643922630363</v>
       </c>
       <c r="J6" s="26" t="n">
         <f aca="false">J79</f>
@@ -39008,7 +39008,7 @@
       </c>
       <c r="F9" s="18" t="n">
         <f aca="false">F80</f>
-        <v>0.720730287080741</v>
+        <v>0.720730287080742</v>
       </c>
       <c r="G9" s="18" t="n">
         <f aca="false">G80</f>
@@ -39068,7 +39068,7 @@
       </c>
       <c r="G11" s="17" t="n">
         <f aca="false">G91</f>
-        <v>0.0746351605280453</v>
+        <v>0.0746351605280452</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -39104,7 +39104,7 @@
       </c>
       <c r="I12" s="25" t="n">
         <f aca="false">I93</f>
-        <v>192.964661844076</v>
+        <v>192.964661844077</v>
       </c>
       <c r="J12" s="25" t="n">
         <f aca="false">J93</f>
@@ -39128,7 +39128,7 @@
       </c>
       <c r="E13" s="17" t="n">
         <f aca="false">E97</f>
-        <v>0.0533014396086032</v>
+        <v>0.0533014396086033</v>
       </c>
       <c r="F13" s="17" t="n">
         <f aca="false">F97</f>
@@ -39172,7 +39172,7 @@
       </c>
       <c r="F14" s="19" t="n">
         <f aca="false">F95</f>
-        <v>290.948676812537</v>
+        <v>290.948676812538</v>
       </c>
       <c r="G14" s="19" t="n">
         <f aca="false">G95</f>
@@ -39204,15 +39204,15 @@
       </c>
       <c r="E15" s="18" t="n">
         <f aca="false">E96</f>
-        <v>0.737612235441472</v>
+        <v>0.737612235441474</v>
       </c>
       <c r="F15" s="18" t="n">
         <f aca="false">F96</f>
-        <v>0.208668076527857</v>
+        <v>0.208668076527856</v>
       </c>
       <c r="G15" s="18" t="n">
         <f aca="false">G96</f>
-        <v>0.07428335499381</v>
+        <v>0.0742833549938098</v>
       </c>
       <c r="H15" s="26" t="n">
         <f aca="false">H96</f>
@@ -39220,11 +39220,11 @@
       </c>
       <c r="I15" s="26" t="n">
         <f aca="false">I96</f>
-        <v>0.045337703744315</v>
+        <v>0.0453377037443146</v>
       </c>
       <c r="J15" s="26" t="n">
         <f aca="false">J96</f>
-        <v>0.0547263681592041</v>
+        <v>0.0547263681592043</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -39253,7 +39253,7 @@
       </c>
       <c r="F18" s="22" t="n">
         <f aca="false">F118</f>
-        <v>2513.97917367725</v>
+        <v>2513.97917367726</v>
       </c>
       <c r="G18" s="22" t="n">
         <f aca="false">G118</f>
@@ -39285,23 +39285,23 @@
       </c>
       <c r="E19" s="18" t="n">
         <f aca="false">E119</f>
-        <v>0.730205547569951</v>
+        <v>0.730205547569952</v>
       </c>
       <c r="F19" s="18" t="n">
         <f aca="false">F119</f>
-        <v>-0.00388843053794075</v>
+        <v>-0.00388843053794052</v>
       </c>
       <c r="G19" s="18" t="n">
         <f aca="false">G119</f>
-        <v>0.0750506893021918</v>
+        <v>0.0750506893021916</v>
       </c>
       <c r="H19" s="26" t="n">
         <f aca="false">H119</f>
-        <v>0.0633671262014612</v>
+        <v>0.0633671262014611</v>
       </c>
       <c r="I19" s="26" t="n">
         <f aca="false">I119</f>
-        <v>0.0516835631007306</v>
+        <v>0.0516835631007305</v>
       </c>
       <c r="J19" s="26" t="n">
         <f aca="false">J119</f>
@@ -39329,7 +39329,7 @@
       </c>
       <c r="F20" s="22" t="n">
         <f aca="false">F115</f>
-        <v>1693.65434115005</v>
+        <v>1693.65434115006</v>
       </c>
       <c r="G20" s="22" t="n">
         <f aca="false">G115</f>
@@ -39389,7 +39389,7 @@
       </c>
       <c r="G22" s="18" t="n">
         <f aca="false">G120</f>
-        <v>0.687368693419264</v>
+        <v>0.687368693419265</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -39469,11 +39469,11 @@
       </c>
       <c r="F25" s="22" t="n">
         <f aca="false">F133</f>
-        <v>139.366088497109</v>
+        <v>139.36608849711</v>
       </c>
       <c r="G25" s="22" t="n">
         <f aca="false">G133</f>
-        <v>156.613098788618</v>
+        <v>156.613098788619</v>
       </c>
       <c r="H25" s="25" t="n">
         <f aca="false">H133</f>
@@ -39485,7 +39485,7 @@
       </c>
       <c r="J25" s="25" t="n">
         <f aca="false">J133</f>
-        <v>153.709110250491</v>
+        <v>153.709110250492</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -39505,7 +39505,7 @@
       </c>
       <c r="E26" s="17" t="n">
         <f aca="false">E137</f>
-        <v>0.0533014396086032</v>
+        <v>0.0533014396086033</v>
       </c>
       <c r="F26" s="17" t="n">
         <f aca="false">F137</f>
@@ -39525,7 +39525,7 @@
       </c>
       <c r="J26" s="27" t="n">
         <f aca="false">J137</f>
-        <v>0.0488998284347512</v>
+        <v>0.0488998284347513</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -39581,11 +39581,11 @@
       </c>
       <c r="E28" s="18" t="n">
         <f aca="false">E136</f>
-        <v>0.737612235441472</v>
+        <v>0.737612235441474</v>
       </c>
       <c r="F28" s="18" t="n">
         <f aca="false">F136</f>
-        <v>0.0308569876471492</v>
+        <v>0.0308569876471489</v>
       </c>
       <c r="G28" s="18" t="n">
         <f aca="false">G136</f>
@@ -39593,15 +39593,15 @@
       </c>
       <c r="H28" s="26" t="n">
         <f aca="false">H136</f>
-        <v>0.00300701105188117</v>
+        <v>0.00300701105188095</v>
       </c>
       <c r="I28" s="26" t="n">
         <f aca="false">I136</f>
-        <v>-0.0110037179531206</v>
+        <v>-0.0110037179531208</v>
       </c>
       <c r="J28" s="26" t="n">
         <f aca="false">J136</f>
-        <v>-0.025291590715105</v>
+        <v>-0.0252915907151049</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -39638,7 +39638,7 @@
       </c>
       <c r="H31" s="25" t="n">
         <f aca="false">H158</f>
-        <v>2215.819047873</v>
+        <v>2215.81904787301</v>
       </c>
       <c r="I31" s="25" t="n">
         <f aca="false">I158</f>
@@ -39662,7 +39662,7 @@
       </c>
       <c r="E32" s="18" t="n">
         <f aca="false">E159</f>
-        <v>0.730205547569951</v>
+        <v>0.730205547569952</v>
       </c>
       <c r="F32" s="18" t="n">
         <f aca="false">F159</f>
@@ -39670,15 +39670,15 @@
       </c>
       <c r="G32" s="18" t="n">
         <f aca="false">G159</f>
-        <v>0.0314274200056475</v>
+        <v>0.0314274200056472</v>
       </c>
       <c r="H32" s="26" t="n">
         <f aca="false">H159</f>
-        <v>0.027618280003765</v>
+        <v>0.0276182800037648</v>
       </c>
       <c r="I32" s="26" t="n">
         <f aca="false">I159</f>
-        <v>0.0238091400018825</v>
+        <v>0.0238091400018824</v>
       </c>
       <c r="J32" s="26" t="n">
         <f aca="false">J159</f>
@@ -39766,7 +39766,7 @@
       </c>
       <c r="G35" s="18" t="n">
         <f aca="false">G160</f>
-        <v>0.608149312515919</v>
+        <v>0.60814931251592</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -39882,7 +39882,7 @@
       </c>
       <c r="E39" s="17" t="n">
         <f aca="false">E177</f>
-        <v>0.0533014396086032</v>
+        <v>0.0533014396086033</v>
       </c>
       <c r="F39" s="17" t="n">
         <f aca="false">F177</f>
@@ -39890,7 +39890,7 @@
       </c>
       <c r="G39" s="17" t="n">
         <f aca="false">G177</f>
-        <v>0.0556263367290927</v>
+        <v>0.0556263367290928</v>
       </c>
       <c r="H39" s="27" t="n">
         <f aca="false">H177</f>
@@ -39958,7 +39958,7 @@
       </c>
       <c r="E41" s="18" t="n">
         <f aca="false">E176</f>
-        <v>0.737612235441472</v>
+        <v>0.737612235441474</v>
       </c>
       <c r="F41" s="18" t="n">
         <f aca="false">F176</f>
@@ -39966,11 +39966,11 @@
       </c>
       <c r="G41" s="18" t="n">
         <f aca="false">G176</f>
-        <v>0.0686734567843541</v>
+        <v>0.0686734567843539</v>
       </c>
       <c r="H41" s="26" t="n">
         <f aca="false">H176</f>
-        <v>-0.0741485032238417</v>
+        <v>-0.0741485032238418</v>
       </c>
       <c r="I41" s="26" t="n">
         <f aca="false">I176</f>
@@ -40067,7 +40067,7 @@
       </c>
       <c r="D63" s="30" t="n">
         <f aca="false">itc_26</f>
-        <v>781.872916666667</v>
+        <v>781.872916666666</v>
       </c>
       <c r="E63" s="30" t="n">
         <f aca="false">itc_27*1</f>
@@ -40166,7 +40166,7 @@
       </c>
       <c r="D67" s="22" t="n">
         <f aca="false">D65*D66</f>
-        <v>634.616531285011</v>
+        <v>634.61653128501</v>
       </c>
       <c r="E67" s="22" t="n">
         <f aca="false">E65*E66</f>
@@ -40190,7 +40190,7 @@
       </c>
       <c r="D68" s="22" t="n">
         <f aca="false">D67*fx</f>
-        <v>20307.7290011204</v>
+        <v>20307.7290011203</v>
       </c>
       <c r="E68" s="22" t="n">
         <f aca="false">E67*fx</f>
@@ -40284,15 +40284,15 @@
       </c>
       <c r="E72" s="17" t="n">
         <f aca="false">$D$69*E70*E71</f>
-        <v>0.0498832807117864</v>
+        <v>0.0498832807117865</v>
       </c>
       <c r="F72" s="17" t="n">
         <f aca="false">$D$69*F70*F71</f>
-        <v>0.0509096185694461</v>
+        <v>0.0509096185694462</v>
       </c>
       <c r="G72" s="17" t="n">
         <f aca="false">$D$69*G70*G71</f>
-        <v>0.0488501692055052</v>
+        <v>0.0488501692055053</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -40444,7 +40444,7 @@
       </c>
       <c r="J78" s="25" t="n">
         <f aca="false">I78*(1+J79)</f>
-        <v>3513.54543594395</v>
+        <v>3513.54543594396</v>
       </c>
       <c r="K78" s="8" t="s">
         <v>457</v>
@@ -40463,7 +40463,7 @@
       </c>
       <c r="E79" s="18" t="n">
         <f aca="false">E78/D78-1</f>
-        <v>0.730205547569951</v>
+        <v>0.730205547569952</v>
       </c>
       <c r="F79" s="18" t="n">
         <f aca="false">F78/E78-1</f>
@@ -40471,15 +40471,15 @@
       </c>
       <c r="G79" s="18" t="n">
         <f aca="false">G78/F78-1</f>
-        <v>0.0316931767891091</v>
+        <v>0.0316931767891089</v>
       </c>
       <c r="H79" s="26" t="n">
         <f aca="false">$G79+(fade_gA-$G79)*1/3</f>
-        <v>0.0411287845260727</v>
+        <v>0.0411287845260726</v>
       </c>
       <c r="I79" s="26" t="n">
         <f aca="false">$G79+(fade_gA-$G79)*2/3</f>
-        <v>0.0505643922630364</v>
+        <v>0.0505643922630363</v>
       </c>
       <c r="J79" s="26" t="n">
         <f aca="false">$G79+(fade_gA-$G79)*3/3</f>
@@ -40507,7 +40507,7 @@
       </c>
       <c r="F80" s="18" t="n">
         <f aca="false">F75/F78</f>
-        <v>0.720730287080741</v>
+        <v>0.720730287080742</v>
       </c>
       <c r="G80" s="18" t="n">
         <f aca="false">G75/G78</f>
@@ -40523,7 +40523,7 @@
       </c>
       <c r="D81" s="23" t="n">
         <f aca="false">D75/fx/D65</f>
-        <v>0.935061049524468</v>
+        <v>0.935061049524469</v>
       </c>
       <c r="E81" s="23" t="n">
         <f aca="false">E75/fx/E65</f>
@@ -40575,7 +40575,7 @@
       </c>
       <c r="F84" s="30" t="n">
         <f aca="false">($D$83+d_ai+vrd)*F73*(1-F74*(1-keep))</f>
-        <v>177.480793184849</v>
+        <v>177.48079318485</v>
       </c>
       <c r="G84" s="30" t="n">
         <f aca="false">($D$83+d_ai+vrd)*G73*(1-G74*(1-keep))</f>
@@ -40685,11 +40685,11 @@
       </c>
       <c r="E88" s="22" t="n">
         <f aca="false">D88*(1+MAX(0,phi*E79))</f>
-        <v>35.6727317290002</v>
+        <v>35.6727317290003</v>
       </c>
       <c r="F88" s="22" t="n">
         <f aca="false">E88*(1+MAX(0,phi*F79))</f>
-        <v>40.3495789783962</v>
+        <v>40.3495789783963</v>
       </c>
       <c r="G88" s="22" t="n">
         <f aca="false">F88*(1+MAX(0,phi*G79))</f>
@@ -40713,11 +40713,11 @@
       </c>
       <c r="E89" s="22" t="n">
         <f aca="false">E88+0*E78</f>
-        <v>35.6727317290002</v>
+        <v>35.6727317290003</v>
       </c>
       <c r="F89" s="22" t="n">
         <f aca="false">F88+0*F78</f>
-        <v>40.3495789783962</v>
+        <v>40.3495789783963</v>
       </c>
       <c r="G89" s="22" t="n">
         <f aca="false">G88+0*G78</f>
@@ -40745,7 +40745,7 @@
       </c>
       <c r="F90" s="22" t="n">
         <f aca="false">F85-F89</f>
-        <v>209.493783819765</v>
+        <v>209.493783819766</v>
       </c>
       <c r="G90" s="22" t="n">
         <f aca="false">G85-G89</f>
@@ -40777,7 +40777,7 @@
       </c>
       <c r="G91" s="17" t="n">
         <f aca="false">G90/G78</f>
-        <v>0.0746351605280453</v>
+        <v>0.0746351605280452</v>
       </c>
     </row>
     <row r="92" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -40841,7 +40841,7 @@
       </c>
       <c r="I93" s="25" t="n">
         <f aca="false">I78*I97</f>
-        <v>192.964661844076</v>
+        <v>192.964661844077</v>
       </c>
       <c r="J93" s="25" t="n">
         <f aca="false">J78*J97</f>
@@ -40909,7 +40909,7 @@
       </c>
       <c r="F95" s="30" t="n">
         <f aca="false">F93/F94</f>
-        <v>290.948676812537</v>
+        <v>290.948676812538</v>
       </c>
       <c r="G95" s="30" t="n">
         <f aca="false">G93/G94</f>
@@ -40941,15 +40941,15 @@
       </c>
       <c r="E96" s="18" t="n">
         <f aca="false">E95/D95-1</f>
-        <v>0.737612235441472</v>
+        <v>0.737612235441474</v>
       </c>
       <c r="F96" s="18" t="n">
         <f aca="false">F95/E95-1</f>
-        <v>0.208668076527857</v>
+        <v>0.208668076527856</v>
       </c>
       <c r="G96" s="18" t="n">
         <f aca="false">G95/F95-1</f>
-        <v>0.07428335499381</v>
+        <v>0.0742833549938098</v>
       </c>
       <c r="H96" s="26" t="n">
         <f aca="false">H95/G95-1</f>
@@ -40957,11 +40957,11 @@
       </c>
       <c r="I96" s="26" t="n">
         <f aca="false">I95/H95-1</f>
-        <v>0.045337703744315</v>
+        <v>0.0453377037443146</v>
       </c>
       <c r="J96" s="26" t="n">
         <f aca="false">J95/I95-1</f>
-        <v>0.0547263681592041</v>
+        <v>0.0547263681592043</v>
       </c>
     </row>
     <row r="97" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -40981,7 +40981,7 @@
       </c>
       <c r="E97" s="17" t="n">
         <f aca="false">E93/E78</f>
-        <v>0.0533014396086032</v>
+        <v>0.0533014396086033</v>
       </c>
       <c r="F97" s="17" t="n">
         <f aca="false">F93/F78</f>
@@ -41058,7 +41058,7 @@
       </c>
       <c r="D103" s="30" t="n">
         <f aca="false">itc_26</f>
-        <v>781.872916666667</v>
+        <v>781.872916666666</v>
       </c>
       <c r="E103" s="30" t="n">
         <f aca="false">itc_27*1</f>
@@ -41157,7 +41157,7 @@
       </c>
       <c r="D107" s="22" t="n">
         <f aca="false">D105*D106</f>
-        <v>634.616531285011</v>
+        <v>634.61653128501</v>
       </c>
       <c r="E107" s="22" t="n">
         <f aca="false">E105*E106</f>
@@ -41181,7 +41181,7 @@
       </c>
       <c r="D108" s="22" t="n">
         <f aca="false">D107*fx</f>
-        <v>20307.7290011204</v>
+        <v>20307.7290011203</v>
       </c>
       <c r="E108" s="22" t="n">
         <f aca="false">E107*fx</f>
@@ -41275,15 +41275,15 @@
       </c>
       <c r="E112" s="17" t="n">
         <f aca="false">$D$109*E110*E111</f>
-        <v>0.0498832807117864</v>
+        <v>0.0498832807117865</v>
       </c>
       <c r="F112" s="17" t="n">
         <f aca="false">$D$109*F110*F111</f>
-        <v>0.0509096185694461</v>
+        <v>0.0509096185694462</v>
       </c>
       <c r="G112" s="17" t="n">
         <f aca="false">$D$109*G110*G111</f>
-        <v>0.0488501692055052</v>
+        <v>0.0488501692055053</v>
       </c>
     </row>
     <row r="113" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -41303,7 +41303,7 @@
       </c>
       <c r="F113" s="22" t="n">
         <f aca="false">F108*F112</f>
-        <v>1881.83815683339</v>
+        <v>1881.8381568334</v>
       </c>
       <c r="G113" s="22" t="n">
         <f aca="false">G108*G112</f>
@@ -41358,7 +41358,7 @@
       </c>
       <c r="F115" s="22" t="n">
         <f aca="false">F113*(1-F114)</f>
-        <v>1693.65434115005</v>
+        <v>1693.65434115006</v>
       </c>
       <c r="G115" s="22" t="n">
         <f aca="false">G113*(1-G114)</f>
@@ -41419,7 +41419,7 @@
       </c>
       <c r="F118" s="22" t="n">
         <f aca="false">F115+F117</f>
-        <v>2513.97917367725</v>
+        <v>2513.97917367726</v>
       </c>
       <c r="G118" s="22" t="n">
         <f aca="false">G115+G117</f>
@@ -41454,23 +41454,23 @@
       </c>
       <c r="E119" s="18" t="n">
         <f aca="false">E118/D118-1</f>
-        <v>0.730205547569951</v>
+        <v>0.730205547569952</v>
       </c>
       <c r="F119" s="18" t="n">
         <f aca="false">F118/E118-1</f>
-        <v>-0.00388843053794075</v>
+        <v>-0.00388843053794052</v>
       </c>
       <c r="G119" s="18" t="n">
         <f aca="false">G118/F118-1</f>
-        <v>0.0750506893021918</v>
+        <v>0.0750506893021916</v>
       </c>
       <c r="H119" s="26" t="n">
         <f aca="false">$G119+(fade_gB-$G119)*1/3</f>
-        <v>0.0633671262014612</v>
+        <v>0.0633671262014611</v>
       </c>
       <c r="I119" s="26" t="n">
         <f aca="false">$G119+(fade_gB-$G119)*2/3</f>
-        <v>0.0516835631007306</v>
+        <v>0.0516835631007305</v>
       </c>
       <c r="J119" s="26" t="n">
         <f aca="false">$G119+(fade_gB-$G119)*3/3</f>
@@ -41502,7 +41502,7 @@
       </c>
       <c r="G120" s="18" t="n">
         <f aca="false">G115/G118</f>
-        <v>0.687368693419264</v>
+        <v>0.687368693419265</v>
       </c>
     </row>
     <row r="121" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -41514,7 +41514,7 @@
       </c>
       <c r="D121" s="23" t="n">
         <f aca="false">D115/fx/D105</f>
-        <v>0.935061049524468</v>
+        <v>0.935061049524469</v>
       </c>
       <c r="E121" s="23" t="n">
         <f aca="false">E115/fx/E105</f>
@@ -41676,11 +41676,11 @@
       </c>
       <c r="E128" s="22" t="n">
         <f aca="false">D128*(1+MAX(0,phi*E119))</f>
-        <v>35.6727317290002</v>
+        <v>35.6727317290003</v>
       </c>
       <c r="F128" s="22" t="n">
         <f aca="false">E128*(1+MAX(0,phi*F119))</f>
-        <v>35.6727317290002</v>
+        <v>35.6727317290003</v>
       </c>
       <c r="G128" s="22" t="n">
         <f aca="false">F128*(1+MAX(0,phi*G119))</f>
@@ -41704,11 +41704,11 @@
       </c>
       <c r="E129" s="22" t="n">
         <f aca="false">E128+0*E118</f>
-        <v>35.6727317290002</v>
+        <v>35.6727317290003</v>
       </c>
       <c r="F129" s="22" t="n">
         <f aca="false">F128+0*F118</f>
-        <v>35.6727317290002</v>
+        <v>35.6727317290003</v>
       </c>
       <c r="G129" s="22" t="n">
         <f aca="false">G128+0*G118</f>
@@ -41736,11 +41736,11 @@
       </c>
       <c r="F130" s="22" t="n">
         <f aca="false">F125-F129</f>
-        <v>178.674472432191</v>
+        <v>178.674472432192</v>
       </c>
       <c r="G130" s="22" t="n">
         <f aca="false">G125-G129</f>
-        <v>200.786024087972</v>
+        <v>200.786024087973</v>
       </c>
     </row>
     <row r="131" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -41820,11 +41820,11 @@
       </c>
       <c r="F133" s="22" t="n">
         <f aca="false">F130*F132</f>
-        <v>139.366088497109</v>
+        <v>139.36608849711</v>
       </c>
       <c r="G133" s="22" t="n">
         <f aca="false">G130*G132</f>
-        <v>156.613098788618</v>
+        <v>156.613098788619</v>
       </c>
       <c r="H133" s="25" t="n">
         <f aca="false">H118*H137</f>
@@ -41836,7 +41836,7 @@
       </c>
       <c r="J133" s="25" t="n">
         <f aca="false">J118*J137</f>
-        <v>153.709110250491</v>
+        <v>153.709110250492</v>
       </c>
     </row>
     <row r="134" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -41932,11 +41932,11 @@
       </c>
       <c r="E136" s="18" t="n">
         <f aca="false">E135/D135-1</f>
-        <v>0.737612235441472</v>
+        <v>0.737612235441474</v>
       </c>
       <c r="F136" s="18" t="n">
         <f aca="false">F135/E135-1</f>
-        <v>0.0308569876471492</v>
+        <v>0.0308569876471489</v>
       </c>
       <c r="G136" s="18" t="n">
         <f aca="false">G135/F135-1</f>
@@ -41944,15 +41944,15 @@
       </c>
       <c r="H136" s="26" t="n">
         <f aca="false">H135/G135-1</f>
-        <v>0.00300701105188117</v>
+        <v>0.00300701105188095</v>
       </c>
       <c r="I136" s="26" t="n">
         <f aca="false">I135/H135-1</f>
-        <v>-0.0110037179531206</v>
+        <v>-0.0110037179531208</v>
       </c>
       <c r="J136" s="26" t="n">
         <f aca="false">J135/I135-1</f>
-        <v>-0.025291590715105</v>
+        <v>-0.0252915907151049</v>
       </c>
     </row>
     <row r="137" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -41972,7 +41972,7 @@
       </c>
       <c r="E137" s="17" t="n">
         <f aca="false">E133/E118</f>
-        <v>0.0533014396086032</v>
+        <v>0.0533014396086033</v>
       </c>
       <c r="F137" s="17" t="n">
         <f aca="false">F133/F118</f>
@@ -41992,7 +41992,7 @@
       </c>
       <c r="J137" s="27" t="n">
         <f aca="false">$G137+(fade_mB-$G137)*3/3</f>
-        <v>0.0488998284347512</v>
+        <v>0.0488998284347513</v>
       </c>
     </row>
     <row r="140" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -42049,7 +42049,7 @@
       </c>
       <c r="D143" s="30" t="n">
         <f aca="false">itc_26</f>
-        <v>781.872916666667</v>
+        <v>781.872916666666</v>
       </c>
       <c r="E143" s="30" t="n">
         <f aca="false">itc_27*1</f>
@@ -42148,7 +42148,7 @@
       </c>
       <c r="D147" s="22" t="n">
         <f aca="false">D145*D146</f>
-        <v>634.616531285011</v>
+        <v>634.61653128501</v>
       </c>
       <c r="E147" s="22" t="n">
         <f aca="false">E145*E146</f>
@@ -42172,7 +42172,7 @@
       </c>
       <c r="D148" s="22" t="n">
         <f aca="false">D147*fx</f>
-        <v>20307.7290011204</v>
+        <v>20307.7290011203</v>
       </c>
       <c r="E148" s="22" t="n">
         <f aca="false">E147*fx</f>
@@ -42266,15 +42266,15 @@
       </c>
       <c r="E152" s="17" t="n">
         <f aca="false">$D$149*E150*E151</f>
-        <v>0.0498832807117864</v>
+        <v>0.0498832807117865</v>
       </c>
       <c r="F152" s="17" t="n">
         <f aca="false">$D$149*F150*F151</f>
-        <v>0.0509096185694461</v>
+        <v>0.0509096185694462</v>
       </c>
       <c r="G152" s="17" t="n">
         <f aca="false">$D$149*G150*G151</f>
-        <v>0.0488501692055052</v>
+        <v>0.0488501692055053</v>
       </c>
     </row>
     <row r="153" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -42294,7 +42294,7 @@
       </c>
       <c r="F153" s="22" t="n">
         <f aca="false">F148*F152</f>
-        <v>1411.37861762504</v>
+        <v>1411.37861762505</v>
       </c>
       <c r="G153" s="22" t="n">
         <f aca="false">G148*G152</f>
@@ -42418,7 +42418,7 @@
       </c>
       <c r="H158" s="25" t="n">
         <f aca="false">G158*(1+H159)</f>
-        <v>2215.819047873</v>
+        <v>2215.81904787301</v>
       </c>
       <c r="I158" s="25" t="n">
         <f aca="false">H158*(1+I159)</f>
@@ -42445,7 +42445,7 @@
       </c>
       <c r="E159" s="18" t="n">
         <f aca="false">E158/D158-1</f>
-        <v>0.730205547569951</v>
+        <v>0.730205547569952</v>
       </c>
       <c r="F159" s="18" t="n">
         <f aca="false">F158/E158-1</f>
@@ -42453,15 +42453,15 @@
       </c>
       <c r="G159" s="18" t="n">
         <f aca="false">G158/F158-1</f>
-        <v>0.0314274200056475</v>
+        <v>0.0314274200056472</v>
       </c>
       <c r="H159" s="26" t="n">
         <f aca="false">$G159+(fade_gC-$G159)*1/3</f>
-        <v>0.027618280003765</v>
+        <v>0.0276182800037648</v>
       </c>
       <c r="I159" s="26" t="n">
         <f aca="false">$G159+(fade_gC-$G159)*2/3</f>
-        <v>0.0238091400018825</v>
+        <v>0.0238091400018824</v>
       </c>
       <c r="J159" s="26" t="n">
         <f aca="false">$G159+(fade_gC-$G159)*3/3</f>
@@ -42493,7 +42493,7 @@
       </c>
       <c r="G160" s="18" t="n">
         <f aca="false">G155/G158</f>
-        <v>0.608149312515919</v>
+        <v>0.60814931251592</v>
       </c>
     </row>
     <row r="161" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -42505,7 +42505,7 @@
       </c>
       <c r="D161" s="23" t="n">
         <f aca="false">D155/fx/D145</f>
-        <v>0.935061049524468</v>
+        <v>0.935061049524469</v>
       </c>
       <c r="E161" s="23" t="n">
         <f aca="false">E155/fx/E145</f>
@@ -42561,7 +42561,7 @@
       </c>
       <c r="G164" s="30" t="n">
         <f aca="false">($D$163+d_ai+vrd)*G153*(1-G154*(1-keep))</f>
-        <v>115.81208442332</v>
+        <v>115.812084423321</v>
       </c>
       <c r="K164" s="4" t="s">
         <v>464</v>
@@ -42667,11 +42667,11 @@
       </c>
       <c r="E168" s="22" t="n">
         <f aca="false">D168*(1+MAX(0,phi*E159))</f>
-        <v>35.6727317290002</v>
+        <v>35.6727317290003</v>
       </c>
       <c r="F168" s="22" t="n">
         <f aca="false">E168*(1+MAX(0,phi*F159))</f>
-        <v>35.6727317290002</v>
+        <v>35.6727317290003</v>
       </c>
       <c r="G168" s="22" t="n">
         <f aca="false">F168*(1+MAX(0,phi*G159))</f>
@@ -42695,11 +42695,11 @@
       </c>
       <c r="E169" s="22" t="n">
         <f aca="false">E168+0*E158</f>
-        <v>35.6727317290002</v>
+        <v>35.6727317290003</v>
       </c>
       <c r="F169" s="22" t="n">
         <f aca="false">F168+0*F158</f>
-        <v>35.6727317290002</v>
+        <v>35.6727317290003</v>
       </c>
       <c r="G169" s="22" t="n">
         <f aca="false">G168+0*G158</f>
@@ -42923,7 +42923,7 @@
       </c>
       <c r="E176" s="18" t="n">
         <f aca="false">E175/D175-1</f>
-        <v>0.737612235441472</v>
+        <v>0.737612235441474</v>
       </c>
       <c r="F176" s="18" t="n">
         <f aca="false">F175/E175-1</f>
@@ -42931,11 +42931,11 @@
       </c>
       <c r="G176" s="18" t="n">
         <f aca="false">G175/F175-1</f>
-        <v>0.0686734567843541</v>
+        <v>0.0686734567843539</v>
       </c>
       <c r="H176" s="26" t="n">
         <f aca="false">H175/G175-1</f>
-        <v>-0.0741485032238417</v>
+        <v>-0.0741485032238418</v>
       </c>
       <c r="I176" s="26" t="n">
         <f aca="false">I175/H175-1</f>
@@ -42963,7 +42963,7 @@
       </c>
       <c r="E177" s="17" t="n">
         <f aca="false">E173/E158</f>
-        <v>0.0533014396086032</v>
+        <v>0.0533014396086033</v>
       </c>
       <c r="F177" s="17" t="n">
         <f aca="false">F173/F158</f>
@@ -42971,7 +42971,7 @@
       </c>
       <c r="G177" s="17" t="n">
         <f aca="false">G173/G158</f>
-        <v>0.0556263367290927</v>
+        <v>0.0556263367290928</v>
       </c>
       <c r="H177" s="27" t="n">
         <f aca="false">$G177+(fade_mC-$G177)*1/3</f>
@@ -43077,7 +43077,7 @@
       </c>
       <c r="B9" s="19" t="n">
         <f aca="false">PL!F14</f>
-        <v>290.948676812537</v>
+        <v>290.948676812538</v>
       </c>
       <c r="C9" s="19" t="n">
         <f aca="false">PL!F27</f>
@@ -43204,7 +43204,7 @@
       </c>
       <c r="D17" s="19" t="n">
         <f aca="false">D9*(1-$B$15)</f>
-        <v>177.656899781352</v>
+        <v>177.656899781353</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -43221,7 +43221,7 @@
       </c>
       <c r="D18" s="19" t="n">
         <f aca="false">D10*(1-$B$15)</f>
-        <v>189.857213210929</v>
+        <v>189.85721321093</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -43467,7 +43467,7 @@
       </c>
       <c r="B34" s="19" t="n">
         <f aca="false">tp_wA*(2/12*B8+10/12*B9)+tp_wB*(2/12*C8+10/12*C9)+tp_wC*(2/12*D8+10/12*D9)</f>
-        <v>249.392616213047</v>
+        <v>249.392616213048</v>
       </c>
       <c r="E34" s="4" t="s">
         <v>519</v>
@@ -43542,7 +43542,7 @@
       </c>
       <c r="B42" s="18" t="n">
         <f aca="false">B39/px-1</f>
-        <v>0.801317023195681</v>
+        <v>0.801317023195682</v>
       </c>
       <c r="E42" s="4" t="s">
         <v>530</v>
@@ -43554,7 +43554,7 @@
       </c>
       <c r="B43" s="18" t="n">
         <f aca="false">B40/px-1</f>
-        <v>0.56141464063821</v>
+        <v>0.561414640638211</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -43563,7 +43563,7 @@
       </c>
       <c r="B44" s="18" t="n">
         <f aca="false">B34/cons_feps-1</f>
-        <v>0.55605073839311</v>
+        <v>0.556050738393111</v>
       </c>
       <c r="E44" s="4" t="s">
         <v>533</v>
@@ -43679,15 +43679,15 @@
       </c>
       <c r="B55" s="21" t="n">
         <f aca="false">px/PL!E14</f>
-        <v>7.64378544413928</v>
+        <v>7.64378544413927</v>
       </c>
       <c r="C55" s="21" t="n">
         <f aca="false">px/PL!E27</f>
-        <v>7.64378544413928</v>
+        <v>7.64378544413927</v>
       </c>
       <c r="D55" s="21" t="n">
         <f aca="false">px/PL!E40</f>
-        <v>7.64378544413928</v>
+        <v>7.64378544413927</v>
       </c>
       <c r="E55" s="8" t="s">
         <v>549</v>
@@ -43699,7 +43699,7 @@
       </c>
       <c r="B56" s="21" t="n">
         <f aca="false">px/PL!F14</f>
-        <v>6.3241394329679</v>
+        <v>6.32413943296789</v>
       </c>
       <c r="C56" s="21" t="n">
         <f aca="false">px/PL!F27</f>
@@ -43707,7 +43707,7 @@
       </c>
       <c r="D56" s="21" t="n">
         <f aca="false">px/PL!F40</f>
-        <v>9.25327211990428</v>
+        <v>9.25327211990427</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -43720,11 +43720,11 @@
       </c>
       <c r="C57" s="21" t="n">
         <f aca="false">px/PL!G27</f>
-        <v>6.63139899681928</v>
+        <v>6.63139899681927</v>
       </c>
       <c r="D57" s="21" t="n">
         <f aca="false">px/PL!G40</f>
-        <v>8.65865252024453</v>
+        <v>8.65865252024452</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -43742,7 +43742,7 @@
       </c>
       <c r="B59" s="21" t="n">
         <f aca="false">px/B58</f>
-        <v>8.3529466135253</v>
+        <v>8.35294661352529</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -43914,7 +43914,7 @@
       </c>
       <c r="G71" s="37" t="n">
         <f aca="false">px/C71</f>
-        <v>7.64378544413928</v>
+        <v>7.64378544413927</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -43943,7 +43943,7 @@
       </c>
       <c r="G72" s="37" t="n">
         <f aca="false">px/C72</f>
-        <v>7.64378544413928</v>
+        <v>7.64378544413927</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -43968,11 +43968,11 @@
       </c>
       <c r="F73" s="39" t="n">
         <f aca="false">E73/px-1</f>
-        <v>0.87995857615521</v>
+        <v>0.879958576155213</v>
       </c>
       <c r="G73" s="37" t="n">
         <f aca="false">px/C73</f>
-        <v>7.64378544413928</v>
+        <v>7.64378544413927</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -44003,7 +44003,7 @@
       </c>
       <c r="B77" s="21" t="n">
         <f aca="false">px*A77/PL!F14</f>
-        <v>6.3241394329679</v>
+        <v>6.32413943296789</v>
       </c>
       <c r="C77" s="21" t="n">
         <f aca="false">px*A77/PL!F27</f>
@@ -44011,7 +44011,7 @@
       </c>
       <c r="D77" s="21" t="n">
         <f aca="false">px*A77/PL!F40</f>
-        <v>9.25327211990428</v>
+        <v>9.25327211990427</v>
       </c>
       <c r="E77" s="21" t="n">
         <f aca="false">pe_mid</f>
@@ -44028,7 +44028,7 @@
       </c>
       <c r="C78" s="21" t="n">
         <f aca="false">px*A78/PL!F27</f>
-        <v>8.15647959834292</v>
+        <v>8.15647959834291</v>
       </c>
       <c r="D78" s="21" t="n">
         <f aca="false">px*A78/PL!F40</f>
@@ -44045,11 +44045,11 @@
       </c>
       <c r="B79" s="21" t="n">
         <f aca="false">px*A79/PL!F14</f>
-        <v>7.65220871389116</v>
+        <v>7.65220871389115</v>
       </c>
       <c r="C79" s="21" t="n">
         <f aca="false">px*A79/PL!F27</f>
-        <v>8.97212755817721</v>
+        <v>8.9721275581772</v>
       </c>
       <c r="D79" s="21" t="n">
         <f aca="false">px*A79/PL!F40</f>
@@ -44066,7 +44066,7 @@
       </c>
       <c r="B80" s="21" t="n">
         <f aca="false">px*A80/PL!F14</f>
-        <v>9.48620914945185</v>
+        <v>9.48620914945184</v>
       </c>
       <c r="C80" s="21" t="n">
         <f aca="false">px*A80/PL!F27</f>
@@ -44095,7 +44095,7 @@
       </c>
       <c r="D81" s="21" t="n">
         <f aca="false">px*A81/PL!F40</f>
-        <v>18.5065442398086</v>
+        <v>18.5065442398085</v>
       </c>
       <c r="E81" s="21" t="n">
         <f aca="false">pe_mid</f>
@@ -44565,11 +44565,11 @@
       </c>
       <c r="G128" s="18" t="n">
         <f aca="false">F128/px-1</f>
-        <v>0.87995857615521</v>
+        <v>0.879958576155213</v>
       </c>
       <c r="H128" s="19" t="n">
         <f aca="false">px/E128</f>
-        <v>7.64378544413928</v>
+        <v>7.64378544413927</v>
       </c>
     </row>
     <row r="129" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -44600,7 +44600,7 @@
       </c>
       <c r="H129" s="19" t="n">
         <f aca="false">px/E129</f>
-        <v>7.64378544413928</v>
+        <v>7.64378544413927</v>
       </c>
     </row>
     <row r="130" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -44627,11 +44627,11 @@
       </c>
       <c r="G130" s="18" t="n">
         <f aca="false">F130/px-1</f>
-        <v>1.7093905436447</v>
+        <v>1.70939054364471</v>
       </c>
       <c r="H130" s="19" t="n">
         <f aca="false">px/E130</f>
-        <v>7.64378544413928</v>
+        <v>7.64378544413927</v>
       </c>
     </row>
     <row r="134" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -44819,7 +44819,7 @@
       </c>
       <c r="D7" s="18" t="n">
         <f aca="false">C7/B7-1</f>
-        <v>0.0140935077988387</v>
+        <v>0.0140935077988396</v>
       </c>
       <c r="E7" s="22" t="n">
         <f aca="false">PL!E118</f>
@@ -44827,7 +44827,7 @@
       </c>
       <c r="F7" s="18" t="n">
         <f aca="false">E7/B7-1</f>
-        <v>0.0140935077988387</v>
+        <v>0.0140935077988396</v>
       </c>
       <c r="G7" s="22" t="n">
         <f aca="false">PL!E158</f>
@@ -44835,7 +44835,7 @@
       </c>
       <c r="H7" s="18" t="n">
         <f aca="false">G7/B7-1</f>
-        <v>0.0140935077988387</v>
+        <v>0.0140935077988396</v>
       </c>
       <c r="I7" s="8" t="s">
         <v>644</v>
@@ -44855,7 +44855,7 @@
       </c>
       <c r="D8" s="18" t="n">
         <f aca="false">C8/B8-1</f>
-        <v>0.226948530931844</v>
+        <v>0.226948530931846</v>
       </c>
       <c r="E8" s="30" t="n">
         <f aca="false">PL!E135</f>
@@ -44863,7 +44863,7 @@
       </c>
       <c r="F8" s="18" t="n">
         <f aca="false">E8/B8-1</f>
-        <v>0.226948530931844</v>
+        <v>0.226948530931846</v>
       </c>
       <c r="G8" s="30" t="n">
         <f aca="false">PL!E175</f>
@@ -44871,7 +44871,7 @@
       </c>
       <c r="H8" s="18" t="n">
         <f aca="false">G8/B8-1</f>
-        <v>0.226948530931844</v>
+        <v>0.226948530931846</v>
       </c>
       <c r="I8" s="8" t="s">
         <v>644</v>
@@ -44887,11 +44887,11 @@
       </c>
       <c r="C9" s="30" t="n">
         <f aca="false">PL!F95</f>
-        <v>290.948676812537</v>
+        <v>290.948676812538</v>
       </c>
       <c r="D9" s="18" t="n">
         <f aca="false">C9/B9-1</f>
-        <v>0.239798425879874</v>
+        <v>0.239798425879875</v>
       </c>
       <c r="E9" s="30" t="n">
         <f aca="false">PL!F135</f>
@@ -44899,7 +44899,7 @@
       </c>
       <c r="F9" s="18" t="n">
         <f aca="false">E9/B9-1</f>
-        <v>0.0574076501330916</v>
+        <v>0.0574076501330927</v>
       </c>
       <c r="G9" s="30" t="n">
         <f aca="false">PL!F175</f>
@@ -44966,7 +44966,7 @@
       </c>
       <c r="D11" s="18" t="n">
         <f aca="false">C11/B11-1</f>
-        <v>0.0657553090678604</v>
+        <v>0.0657553090678613</v>
       </c>
       <c r="E11" s="22" t="n">
         <f aca="false">PL!E118</f>
@@ -44974,7 +44974,7 @@
       </c>
       <c r="F11" s="18" t="n">
         <f aca="false">E11/B11-1</f>
-        <v>0.0657553090678604</v>
+        <v>0.0657553090678613</v>
       </c>
       <c r="G11" s="22" t="n">
         <f aca="false">PL!E158</f>
@@ -44982,7 +44982,7 @@
       </c>
       <c r="H11" s="18" t="n">
         <f aca="false">G11/B11-1</f>
-        <v>0.0657553090678604</v>
+        <v>0.0657553090678613</v>
       </c>
       <c r="I11" s="4" t="s">
         <v>649</v>
@@ -45002,7 +45002,7 @@
       </c>
       <c r="D12" s="18" t="n">
         <f aca="false">C12/B12-1</f>
-        <v>0.267634654290284</v>
+        <v>0.267634654290286</v>
       </c>
       <c r="E12" s="30" t="n">
         <f aca="false">PL!E135</f>
@@ -45010,7 +45010,7 @@
       </c>
       <c r="F12" s="18" t="n">
         <f aca="false">E12/B12-1</f>
-        <v>0.267634654290284</v>
+        <v>0.267634654290286</v>
       </c>
       <c r="G12" s="30" t="n">
         <f aca="false">PL!E175</f>
@@ -45018,7 +45018,7 @@
       </c>
       <c r="H12" s="18" t="n">
         <f aca="false">G12/B12-1</f>
-        <v>0.267634654290284</v>
+        <v>0.267634654290286</v>
       </c>
       <c r="I12" s="4" t="s">
         <v>649</v>
@@ -45038,7 +45038,7 @@
       </c>
       <c r="D13" s="18" t="n">
         <f aca="false">C13-B13</f>
-        <v>0.0124697514439175</v>
+        <v>0.0124697514439176</v>
       </c>
       <c r="E13" s="17" t="n">
         <f aca="false">PL!E126</f>
@@ -45046,7 +45046,7 @@
       </c>
       <c r="F13" s="18" t="n">
         <f aca="false">E13-B13</f>
-        <v>0.0124697514439175</v>
+        <v>0.0124697514439176</v>
       </c>
       <c r="G13" s="17" t="n">
         <f aca="false">PL!E166</f>
@@ -45054,7 +45054,7 @@
       </c>
       <c r="H13" s="18" t="n">
         <f aca="false">G13-B13</f>
-        <v>0.0124697514439175</v>
+        <v>0.0124697514439176</v>
       </c>
       <c r="I13" s="4" t="s">
         <v>649</v>
@@ -45073,7 +45073,7 @@
       </c>
       <c r="D14" s="18" t="n">
         <f aca="false">C14-B14</f>
-        <v>0.0744305575329766</v>
+        <v>0.074430557532977</v>
       </c>
       <c r="E14" s="18" t="n">
         <f aca="false">PL!E120</f>
@@ -45081,7 +45081,7 @@
       </c>
       <c r="F14" s="18" t="n">
         <f aca="false">E14-B14</f>
-        <v>0.0744305575329766</v>
+        <v>0.074430557532977</v>
       </c>
       <c r="G14" s="18" t="n">
         <f aca="false">PL!E160</f>
@@ -45089,7 +45089,7 @@
       </c>
       <c r="H14" s="18" t="n">
         <f aca="false">G14-B14</f>
-        <v>0.0744305575329766</v>
+        <v>0.074430557532977</v>
       </c>
       <c r="I14" s="4" t="s">
         <v>649</v>
@@ -45129,15 +45129,15 @@
       </c>
       <c r="C17" s="23" t="n">
         <f aca="false">PL!D81</f>
-        <v>0.935061049524468</v>
+        <v>0.935061049524469</v>
       </c>
       <c r="E17" s="23" t="n">
         <f aca="false">PL!D121</f>
-        <v>0.935061049524468</v>
+        <v>0.935061049524469</v>
       </c>
       <c r="G17" s="23" t="n">
         <f aca="false">PL!D161</f>
-        <v>0.935061049524468</v>
+        <v>0.935061049524469</v>
       </c>
       <c r="I17" s="8" t="s">
         <v>135</v>
@@ -45179,7 +45179,7 @@
       </c>
       <c r="D19" s="18" t="n">
         <f aca="false">C19/B19-1</f>
-        <v>0.197892434328786</v>
+        <v>0.197892434328788</v>
       </c>
       <c r="E19" s="22" t="n">
         <f aca="false">PL!E115</f>
@@ -45187,7 +45187,7 @@
       </c>
       <c r="F19" s="18" t="n">
         <f aca="false">E19/B19-1</f>
-        <v>0.197892434328786</v>
+        <v>0.197892434328788</v>
       </c>
       <c r="G19" s="22" t="n">
         <f aca="false">PL!E155</f>
@@ -45195,7 +45195,7 @@
       </c>
       <c r="H19" s="18" t="n">
         <f aca="false">G19/B19-1</f>
-        <v>0.197892434328786</v>
+        <v>0.197892434328788</v>
       </c>
       <c r="I19" s="4" t="s">
         <v>649</v>
@@ -45356,7 +45356,7 @@
       </c>
       <c r="I4" s="19" t="n">
         <f aca="false">PL!F95</f>
-        <v>290.948676812537</v>
+        <v>290.948676812538</v>
       </c>
       <c r="J4" s="18" t="n">
         <f aca="false">I4/I$4-1</f>
@@ -45388,7 +45388,7 @@
       </c>
       <c r="G5" s="22" t="n">
         <f aca="false">F58</f>
-        <v>2513.97917367725</v>
+        <v>2513.97917367726</v>
       </c>
       <c r="H5" s="17" t="n">
         <f aca="false">F66</f>
@@ -45412,7 +45412,7 @@
       </c>
       <c r="C6" s="22" t="n">
         <f aca="false">E98</f>
-        <v>2869.26494460253</v>
+        <v>2869.26494460254</v>
       </c>
       <c r="D6" s="17" t="n">
         <f aca="false">E106</f>
@@ -45424,11 +45424,11 @@
       </c>
       <c r="F6" s="18" t="n">
         <f aca="false">E6/E$4-1</f>
-        <v>0.135157126419532</v>
+        <v>0.135157126419531</v>
       </c>
       <c r="G6" s="22" t="n">
         <f aca="false">F98</f>
-        <v>3360.80634425228</v>
+        <v>3360.80634425229</v>
       </c>
       <c r="H6" s="17" t="n">
         <f aca="false">F106</f>
@@ -45452,7 +45452,7 @@
       </c>
       <c r="C7" s="22" t="n">
         <f aca="false">E138</f>
-        <v>2264.68863299679</v>
+        <v>2264.6886329968</v>
       </c>
       <c r="D7" s="17" t="n">
         <f aca="false">E146</f>
@@ -45476,7 +45476,7 @@
       </c>
       <c r="I7" s="19" t="n">
         <f aca="false">F155</f>
-        <v>237.980894740677</v>
+        <v>237.980894740678</v>
       </c>
       <c r="J7" s="18" t="n">
         <f aca="false">I7/I$4-1</f>
@@ -45504,11 +45504,11 @@
       </c>
       <c r="F8" s="18" t="n">
         <f aca="false">E8/E$4-1</f>
-        <v>0.0675785632097661</v>
+        <v>0.0675785632097654</v>
       </c>
       <c r="G8" s="22" t="n">
         <f aca="false">F178</f>
-        <v>3149.09955160852</v>
+        <v>3149.09955160853</v>
       </c>
       <c r="H8" s="17" t="n">
         <f aca="false">F186</f>
@@ -45520,7 +45520,7 @@
       </c>
       <c r="J8" s="18" t="n">
         <f aca="false">I8/I$4-1</f>
-        <v>0.0726298068391655</v>
+        <v>0.072629806839166</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -45560,7 +45560,7 @@
       </c>
       <c r="J9" s="18" t="n">
         <f aca="false">I9/I$4-1</f>
-        <v>-0.234391247442016</v>
+        <v>-0.234391247442015</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -45572,7 +45572,7 @@
       </c>
       <c r="C10" s="22" t="n">
         <f aca="false">E258</f>
-        <v>2494.15543815304</v>
+        <v>2494.15543815305</v>
       </c>
       <c r="D10" s="17" t="n">
         <f aca="false">E266</f>
@@ -45584,7 +45584,7 @@
       </c>
       <c r="F10" s="18" t="n">
         <f aca="false">E10/E$4-1</f>
-        <v>-0.0115948443730179</v>
+        <v>-0.0115948443730183</v>
       </c>
       <c r="G10" s="22" t="n">
         <f aca="false">F258</f>
@@ -45600,7 +45600,7 @@
       </c>
       <c r="J10" s="18" t="n">
         <f aca="false">I10/I$4-1</f>
-        <v>-0.0130277899462827</v>
+        <v>-0.0130277899462825</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -45612,7 +45612,7 @@
       </c>
       <c r="C11" s="22" t="n">
         <f aca="false">E298</f>
-        <v>2614.70649761064</v>
+        <v>2614.70649761065</v>
       </c>
       <c r="D11" s="17" t="n">
         <f aca="false">E306</f>
@@ -45624,7 +45624,7 @@
       </c>
       <c r="F11" s="18" t="n">
         <f aca="false">E11/E$4-1</f>
-        <v>-0.00249281340804797</v>
+        <v>-0.00249281340804852</v>
       </c>
       <c r="G11" s="22" t="n">
         <f aca="false">F298</f>
@@ -45640,7 +45640,7 @@
       </c>
       <c r="J11" s="18" t="n">
         <f aca="false">I11/I$4-1</f>
-        <v>-0.00445951339666073</v>
+        <v>-0.00445951339666029</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -45660,11 +45660,11 @@
       </c>
       <c r="E12" s="19" t="n">
         <f aca="false">E355</f>
-        <v>241.91855813528</v>
+        <v>241.918558135281</v>
       </c>
       <c r="F12" s="18" t="n">
         <f aca="false">E12/E$4-1</f>
-        <v>0.00498562681609704</v>
+        <v>0.00498562681609682</v>
       </c>
       <c r="G12" s="22" t="n">
         <f aca="false">F338</f>
@@ -45680,7 +45680,7 @@
       </c>
       <c r="J12" s="18" t="n">
         <f aca="false">I12/I$4-1</f>
-        <v>0.00698540761168576</v>
+        <v>0.0069854076116862</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -45704,7 +45704,7 @@
       </c>
       <c r="F13" s="18" t="n">
         <f aca="false">E13/E$4-1</f>
-        <v>-0.00803498985389506</v>
+        <v>-0.00803498985389539</v>
       </c>
       <c r="G13" s="22" t="n">
         <f aca="false">F378</f>
@@ -45716,11 +45716,11 @@
       </c>
       <c r="I13" s="19" t="n">
         <f aca="false">F395</f>
-        <v>285.969111792068</v>
+        <v>285.969111792069</v>
       </c>
       <c r="J13" s="18" t="n">
         <f aca="false">I13/I$4-1</f>
-        <v>-0.0171149258179214</v>
+        <v>-0.017114925817921</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -45800,7 +45800,7 @@
       </c>
       <c r="J15" s="18" t="n">
         <f aca="false">I15/I$4-1</f>
-        <v>0.146583550481153</v>
+        <v>0.146583550481154</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -45824,7 +45824,7 @@
       </c>
       <c r="F16" s="18" t="n">
         <f aca="false">E16/E$4-1</f>
-        <v>-0.0500468639700967</v>
+        <v>-0.0500468639700968</v>
       </c>
       <c r="G16" s="22" t="n">
         <f aca="false">F498</f>
@@ -45836,11 +45836,11 @@
       </c>
       <c r="I16" s="19" t="n">
         <f aca="false">F515</f>
-        <v>272.730616620601</v>
+        <v>272.730616620602</v>
       </c>
       <c r="J16" s="18" t="n">
         <f aca="false">I16/I$4-1</f>
-        <v>-0.0626160613326113</v>
+        <v>-0.0626160613326107</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -45860,11 +45860,11 @@
       </c>
       <c r="E17" s="19" t="n">
         <f aca="false">E555</f>
-        <v>248.749894106613</v>
+        <v>248.749894106614</v>
       </c>
       <c r="F17" s="18" t="n">
         <f aca="false">E17/E$4-1</f>
-        <v>0.0333645759800647</v>
+        <v>0.0333645759800645</v>
       </c>
       <c r="G17" s="22" t="n">
         <f aca="false">F538</f>
@@ -45876,11 +45876,11 @@
       </c>
       <c r="I17" s="19" t="n">
         <f aca="false">F555</f>
-        <v>305.732382436289</v>
+        <v>305.73238243629</v>
       </c>
       <c r="J17" s="18" t="n">
         <f aca="false">I17/I$4-1</f>
-        <v>0.0508120737503039</v>
+        <v>0.0508120737503044</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -45896,7 +45896,7 @@
       </c>
       <c r="D18" s="17" t="n">
         <f aca="false">E586</f>
-        <v>0.0802568598154691</v>
+        <v>0.0802568598154692</v>
       </c>
       <c r="E18" s="19" t="n">
         <f aca="false">E595</f>
@@ -45904,7 +45904,7 @@
       </c>
       <c r="F18" s="18" t="n">
         <f aca="false">E18/E$4-1</f>
-        <v>-0.032382905281064</v>
+        <v>-0.0323829052810645</v>
       </c>
       <c r="G18" s="22" t="n">
         <f aca="false">F578</f>
@@ -45916,11 +45916,11 @@
       </c>
       <c r="I18" s="19" t="n">
         <f aca="false">F595</f>
-        <v>279.599162192864</v>
+        <v>279.599162192865</v>
       </c>
       <c r="J18" s="18" t="n">
         <f aca="false">I18/I$4-1</f>
-        <v>-0.0390086483431081</v>
+        <v>-0.039008648343108</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -45944,7 +45944,7 @@
       </c>
       <c r="F19" s="18" t="n">
         <f aca="false">E19/E$4-1</f>
-        <v>0.0323829052810647</v>
+        <v>0.032382905281064</v>
       </c>
       <c r="G19" s="22" t="n">
         <f aca="false">F618</f>
@@ -45960,7 +45960,7 @@
       </c>
       <c r="J19" s="18" t="n">
         <f aca="false">I19/I$4-1</f>
-        <v>0.039008648343108</v>
+        <v>0.0390086483431085</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -45984,7 +45984,7 @@
       </c>
       <c r="F20" s="18" t="n">
         <f aca="false">E20/E$4-1</f>
-        <v>-0.0314706552177212</v>
+        <v>-0.0314706552177216</v>
       </c>
       <c r="G20" s="22" t="n">
         <f aca="false">F658</f>
@@ -45996,11 +45996,11 @@
       </c>
       <c r="I20" s="19" t="n">
         <f aca="false">F675</f>
-        <v>281.245946104869</v>
+        <v>281.24594610487</v>
       </c>
       <c r="J20" s="18" t="n">
         <f aca="false">I20/I$4-1</f>
-        <v>-0.0333485988455609</v>
+        <v>-0.0333485988455606</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -46024,7 +46024,7 @@
       </c>
       <c r="F21" s="18" t="n">
         <f aca="false">E21/E$4-1</f>
-        <v>-0.0292675021810892</v>
+        <v>-0.0292675021810894</v>
       </c>
       <c r="G21" s="22" t="n">
         <f aca="false">F698</f>
@@ -46040,7 +46040,7 @@
       </c>
       <c r="J21" s="18" t="n">
         <f aca="false">I21/I$4-1</f>
-        <v>-0.0280427677175561</v>
+        <v>-0.0280427677175557</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -46060,11 +46060,11 @@
       </c>
       <c r="E22" s="19" t="n">
         <f aca="false">E755</f>
-        <v>236.12832175549</v>
+        <v>236.128321755491</v>
       </c>
       <c r="F22" s="18" t="n">
         <f aca="false">E22/E$4-1</f>
-        <v>-0.0190683539219271</v>
+        <v>-0.0190683539219273</v>
       </c>
       <c r="G22" s="22" t="n">
         <f aca="false">F738</f>
@@ -46080,7 +46080,7 @@
       </c>
       <c r="J22" s="18" t="n">
         <f aca="false">I22/I$4-1</f>
-        <v>-0.0238515442102698</v>
+        <v>-0.0238515442102696</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -46100,11 +46100,11 @@
       </c>
       <c r="E23" s="19" t="n">
         <f aca="false">E795</f>
-        <v>222.201623904004</v>
+        <v>222.201623904005</v>
       </c>
       <c r="F23" s="18" t="n">
         <f aca="false">E23/E$4-1</f>
-        <v>-0.0769230769230769</v>
+        <v>-0.0769230769230771</v>
       </c>
       <c r="G23" s="22" t="n">
         <f aca="false">F778</f>
@@ -46120,7 +46120,7 @@
       </c>
       <c r="J23" s="18" t="n">
         <f aca="false">I23/I$4-1</f>
-        <v>-0.0769230769230771</v>
+        <v>-0.0769230769230769</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -46148,7 +46148,7 @@
       </c>
       <c r="G24" s="22" t="n">
         <f aca="false">PL!F118</f>
-        <v>2513.97917367725</v>
+        <v>2513.97917367726</v>
       </c>
       <c r="H24" s="17" t="n">
         <f aca="false">PL!F126</f>
@@ -46274,11 +46274,11 @@
       </c>
       <c r="E32" s="36" t="n">
         <f aca="false">tp_w_dcf*C32+(1-tp_w_dcf)*D32</f>
-        <v>3065.21618319838</v>
+        <v>3065.21618319839</v>
       </c>
       <c r="F32" s="18" t="n">
         <f aca="false">E32/E$31-1</f>
-        <v>-0.0751886875090412</v>
+        <v>-0.0751886875090408</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -46298,7 +46298,7 @@
       </c>
       <c r="E33" s="36" t="n">
         <f aca="false">tp_w_dcf*C33+(1-tp_w_dcf)*D33</f>
-        <v>3663.08919098459</v>
+        <v>3663.0891909846</v>
       </c>
       <c r="F33" s="18" t="n">
         <f aca="false">E33/E$31-1</f>
@@ -46326,7 +46326,7 @@
       </c>
       <c r="F34" s="18" t="n">
         <f aca="false">E34/E$31-1</f>
-        <v>0.0645041067185661</v>
+        <v>0.0645041067185663</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -46350,7 +46350,7 @@
       </c>
       <c r="F35" s="18" t="n">
         <f aca="false">E35/E$31-1</f>
-        <v>-0.0448212101839988</v>
+        <v>-0.0448212101839985</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -46367,11 +46367,11 @@
       </c>
       <c r="E36" s="36" t="n">
         <f aca="false">0.3*C36+(1-0.3)*D36</f>
-        <v>3137.85516911775</v>
+        <v>3137.85516911776</v>
       </c>
       <c r="F36" s="18" t="n">
         <f aca="false">E36/E$31-1</f>
-        <v>-0.0532726620507622</v>
+        <v>-0.053272662050762</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -46449,7 +46449,7 @@
       </c>
       <c r="D43" s="30" t="n">
         <f aca="false">itc_26</f>
-        <v>781.872916666667</v>
+        <v>781.872916666666</v>
       </c>
       <c r="E43" s="30" t="n">
         <f aca="false">itc_27*mf_lo</f>
@@ -46548,7 +46548,7 @@
       </c>
       <c r="D47" s="22" t="n">
         <f aca="false">D45*D46</f>
-        <v>634.616531285011</v>
+        <v>634.61653128501</v>
       </c>
       <c r="E47" s="22" t="n">
         <f aca="false">E45*E46</f>
@@ -46572,7 +46572,7 @@
       </c>
       <c r="D48" s="22" t="n">
         <f aca="false">D47*fx</f>
-        <v>20307.7290011204</v>
+        <v>20307.7290011203</v>
       </c>
       <c r="E48" s="22" t="n">
         <f aca="false">E47*fx</f>
@@ -46666,15 +46666,15 @@
       </c>
       <c r="E52" s="17" t="n">
         <f aca="false">$D$49*E50*E51</f>
-        <v>0.0498832807117864</v>
+        <v>0.0498832807117865</v>
       </c>
       <c r="F52" s="17" t="n">
         <f aca="false">$D$49*F50*F51</f>
-        <v>0.0509096185694461</v>
+        <v>0.0509096185694462</v>
       </c>
       <c r="G52" s="17" t="n">
         <f aca="false">$D$49*G50*G51</f>
-        <v>0.0488501692055052</v>
+        <v>0.0488501692055053</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -46690,11 +46690,11 @@
       </c>
       <c r="E53" s="22" t="n">
         <f aca="false">E48*E52</f>
-        <v>1454.61969709651</v>
+        <v>1454.61969709652</v>
       </c>
       <c r="F53" s="22" t="n">
         <f aca="false">F48*F52</f>
-        <v>1881.83815683339</v>
+        <v>1881.8381568334</v>
       </c>
       <c r="G53" s="22" t="n">
         <f aca="false">G48*G52</f>
@@ -46749,7 +46749,7 @@
       </c>
       <c r="F55" s="22" t="n">
         <f aca="false">F53*(1-F54)</f>
-        <v>1693.65434115005</v>
+        <v>1693.65434115006</v>
       </c>
       <c r="G55" s="22" t="n">
         <f aca="false">G53*(1-G54)</f>
@@ -46810,19 +46810,19 @@
       </c>
       <c r="F58" s="22" t="n">
         <f aca="false">F55+F57</f>
-        <v>2513.97917367725</v>
+        <v>2513.97917367726</v>
       </c>
       <c r="G58" s="22" t="n">
         <f aca="false">G55+G57</f>
-        <v>2593.37736907955</v>
+        <v>2593.37736907956</v>
       </c>
       <c r="H58" s="25" t="n">
         <f aca="false">G58*(1+H59)</f>
-        <v>2699.84878516938</v>
+        <v>2699.84878516939</v>
       </c>
       <c r="I58" s="25" t="n">
         <f aca="false">H58*(1+I59)</f>
-        <v>2836.2655550898</v>
+        <v>2836.26555508981</v>
       </c>
       <c r="J58" s="25" t="n">
         <f aca="false">I58*(1+J59)</f>
@@ -46845,7 +46845,7 @@
       </c>
       <c r="E59" s="18" t="n">
         <f aca="false">E58/D58-1</f>
-        <v>0.493364438055961</v>
+        <v>0.493364438055962</v>
       </c>
       <c r="F59" s="18" t="n">
         <f aca="false">F58/E58-1</f>
@@ -46885,7 +46885,7 @@
       </c>
       <c r="E60" s="18" t="n">
         <f aca="false">E55/E58</f>
-        <v>0.634382615464732</v>
+        <v>0.634382615464733</v>
       </c>
       <c r="F60" s="18" t="n">
         <f aca="false">F55/F58</f>
@@ -46893,7 +46893,7 @@
       </c>
       <c r="G60" s="18" t="n">
         <f aca="false">G55/G58</f>
-        <v>0.674195283888475</v>
+        <v>0.674195283888476</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -46905,7 +46905,7 @@
       </c>
       <c r="D61" s="23" t="n">
         <f aca="false">D55/fx/D45</f>
-        <v>0.935061049524468</v>
+        <v>0.935061049524469</v>
       </c>
       <c r="E61" s="23" t="n">
         <f aca="false">E55/fx/E45</f>
@@ -46984,7 +46984,7 @@
       </c>
       <c r="E65" s="22" t="n">
         <f aca="false">$D$63*E57+E64</f>
-        <v>180.560234113082</v>
+        <v>180.560234113083</v>
       </c>
       <c r="F65" s="22" t="n">
         <f aca="false">$D$63*F57+F64</f>
@@ -47127,7 +47127,7 @@
       </c>
       <c r="F70" s="22" t="n">
         <f aca="false">F65-F69</f>
-        <v>179.069576141735</v>
+        <v>179.069576141736</v>
       </c>
       <c r="G70" s="22" t="n">
         <f aca="false">G65-G69</f>
@@ -47295,7 +47295,7 @@
       </c>
       <c r="G75" s="30" t="n">
         <f aca="false">G73/G74</f>
-        <v>266.405088030273</v>
+        <v>266.405088030274</v>
       </c>
       <c r="H75" s="28" t="n">
         <f aca="false">H73/H74</f>
@@ -47323,7 +47323,7 @@
       </c>
       <c r="E76" s="18" t="n">
         <f aca="false">E75/D75-1</f>
-        <v>0.502761558867785</v>
+        <v>0.502761558867787</v>
       </c>
       <c r="F76" s="18" t="n">
         <f aca="false">F75/E75-1</f>
@@ -47335,7 +47335,7 @@
       </c>
       <c r="H76" s="26" t="n">
         <f aca="false">H75/G75-1</f>
-        <v>0.0372666016196075</v>
+        <v>0.037266601619607</v>
       </c>
       <c r="I76" s="26" t="n">
         <f aca="false">I75/H75-1</f>
@@ -47440,7 +47440,7 @@
       </c>
       <c r="D83" s="30" t="n">
         <f aca="false">itc_26</f>
-        <v>781.872916666667</v>
+        <v>781.872916666666</v>
       </c>
       <c r="E83" s="30" t="n">
         <f aca="false">itc_27*mf_hi</f>
@@ -47539,7 +47539,7 @@
       </c>
       <c r="D87" s="22" t="n">
         <f aca="false">D85*D86</f>
-        <v>634.616531285011</v>
+        <v>634.61653128501</v>
       </c>
       <c r="E87" s="22" t="n">
         <f aca="false">E85*E86</f>
@@ -47563,7 +47563,7 @@
       </c>
       <c r="D88" s="22" t="n">
         <f aca="false">D87*fx</f>
-        <v>20307.7290011204</v>
+        <v>20307.7290011203</v>
       </c>
       <c r="E88" s="22" t="n">
         <f aca="false">E87*fx</f>
@@ -47657,15 +47657,15 @@
       </c>
       <c r="E92" s="17" t="n">
         <f aca="false">$D$89*E90*E91</f>
-        <v>0.0498832807117864</v>
+        <v>0.0498832807117865</v>
       </c>
       <c r="F92" s="17" t="n">
         <f aca="false">$D$89*F90*F91</f>
-        <v>0.0509096185694461</v>
+        <v>0.0509096185694462</v>
       </c>
       <c r="G92" s="17" t="n">
         <f aca="false">$D$89*G90*G91</f>
-        <v>0.0488501692055052</v>
+        <v>0.0488501692055053</v>
       </c>
     </row>
     <row r="93" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -47689,7 +47689,7 @@
       </c>
       <c r="G93" s="22" t="n">
         <f aca="false">G88*G92</f>
-        <v>3085.48727925271</v>
+        <v>3085.48727925272</v>
       </c>
     </row>
     <row r="94" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -47736,7 +47736,7 @@
       </c>
       <c r="E95" s="22" t="n">
         <f aca="false">E93*(1-E94)</f>
-        <v>2072.83306836253</v>
+        <v>2072.83306836254</v>
       </c>
       <c r="F95" s="22" t="n">
         <f aca="false">F93*(1-F94)</f>
@@ -47744,7 +47744,7 @@
       </c>
       <c r="G95" s="22" t="n">
         <f aca="false">G93*(1-G94)</f>
-        <v>2622.6641873648</v>
+        <v>2622.66418736481</v>
       </c>
     </row>
     <row r="96" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -47797,11 +47797,11 @@
       </c>
       <c r="E98" s="22" t="n">
         <f aca="false">E95+E97</f>
-        <v>2869.26494460253</v>
+        <v>2869.26494460254</v>
       </c>
       <c r="F98" s="22" t="n">
         <f aca="false">F95+F97</f>
-        <v>3360.80634425228</v>
+        <v>3360.80634425229</v>
       </c>
       <c r="G98" s="22" t="n">
         <f aca="false">G95+G97</f>
@@ -47813,7 +47813,7 @@
       </c>
       <c r="I98" s="25" t="n">
         <f aca="false">H98*(1+I99)</f>
-        <v>3793.06552462741</v>
+        <v>3793.06552462742</v>
       </c>
       <c r="J98" s="25" t="n">
         <f aca="false">I98*(1+J99)</f>
@@ -47836,23 +47836,23 @@
       </c>
       <c r="E99" s="18" t="n">
         <f aca="false">E98/D98-1</f>
-        <v>0.967046657083941</v>
+        <v>0.967046657083943</v>
       </c>
       <c r="F99" s="18" t="n">
         <f aca="false">F98/E98-1</f>
-        <v>0.171312656425961</v>
+        <v>0.171312656425962</v>
       </c>
       <c r="G99" s="18" t="n">
         <f aca="false">G98/F98-1</f>
-        <v>0.0317758328438584</v>
+        <v>0.0317758328438582</v>
       </c>
       <c r="H99" s="26" t="n">
         <f aca="false">$G99+(fade_gA-$G99)*1/3</f>
-        <v>0.0411838885625723</v>
+        <v>0.0411838885625721</v>
       </c>
       <c r="I99" s="26" t="n">
         <f aca="false">$G99+(fade_gA-$G99)*2/3</f>
-        <v>0.0505919442812862</v>
+        <v>0.0505919442812861</v>
       </c>
       <c r="J99" s="26" t="n">
         <f aca="false">$G99+(fade_gA-$G99)*3/3</f>
@@ -47896,7 +47896,7 @@
       </c>
       <c r="D101" s="23" t="n">
         <f aca="false">D95/fx/D85</f>
-        <v>0.935061049524468</v>
+        <v>0.935061049524469</v>
       </c>
       <c r="E101" s="23" t="n">
         <f aca="false">E95/fx/E85</f>
@@ -47948,7 +47948,7 @@
       </c>
       <c r="F104" s="30" t="n">
         <f aca="false">($D$103+d_ai+vrd)*F93*(1-F94*(1-keep))</f>
-        <v>212.976951821819</v>
+        <v>212.97695182182</v>
       </c>
       <c r="G104" s="30" t="n">
         <f aca="false">($D$103+d_ai+vrd)*G93*(1-G94*(1-keep))</f>
@@ -47983,7 +47983,7 @@
       </c>
       <c r="G105" s="22" t="n">
         <f aca="false">$D$103*G97+G104</f>
-        <v>306.157615548352</v>
+        <v>306.157615548353</v>
       </c>
     </row>
     <row r="106" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -48062,11 +48062,11 @@
       </c>
       <c r="F108" s="22" t="n">
         <f aca="false">E108*(1+MAX(0,phi*F99))</f>
-        <v>45.4130361355752</v>
+        <v>45.4130361355753</v>
       </c>
       <c r="G108" s="22" t="n">
         <f aca="false">F108*(1+MAX(0,phi*G99))</f>
-        <v>46.5674657717161</v>
+        <v>46.5674657717162</v>
       </c>
     </row>
     <row r="109" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -48090,11 +48090,11 @@
       </c>
       <c r="F109" s="22" t="n">
         <f aca="false">F108+0*F98</f>
-        <v>45.4130361355752</v>
+        <v>45.4130361355753</v>
       </c>
       <c r="G109" s="22" t="n">
         <f aca="false">G108+0*G98</f>
-        <v>46.5674657717161</v>
+        <v>46.5674657717162</v>
       </c>
     </row>
     <row r="110" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -48118,7 +48118,7 @@
       </c>
       <c r="F110" s="22" t="n">
         <f aca="false">F105-F109</f>
-        <v>239.926485299556</v>
+        <v>239.926485299557</v>
       </c>
       <c r="G110" s="22" t="n">
         <f aca="false">G105-G109</f>
@@ -48142,7 +48142,7 @@
       </c>
       <c r="E111" s="17" t="n">
         <f aca="false">E110/E98</f>
-        <v>0.0682312543229343</v>
+        <v>0.0682312543229342</v>
       </c>
       <c r="F111" s="17" t="n">
         <f aca="false">F110/F98</f>
@@ -48298,7 +48298,7 @@
       </c>
       <c r="J115" s="28" t="n">
         <f aca="false">J113/J114</f>
-        <v>408.5269203282</v>
+        <v>408.526920328201</v>
       </c>
     </row>
     <row r="116" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -48314,7 +48314,7 @@
       </c>
       <c r="E116" s="18" t="n">
         <f aca="false">E115/D115-1</f>
-        <v>0.97246291201516</v>
+        <v>0.972462912015162</v>
       </c>
       <c r="F116" s="18" t="n">
         <f aca="false">F115/E115-1</f>
@@ -48322,11 +48322,11 @@
       </c>
       <c r="G116" s="18" t="n">
         <f aca="false">G115/F115-1</f>
-        <v>0.0765741688403883</v>
+        <v>0.0765741688403885</v>
       </c>
       <c r="H116" s="26" t="n">
         <f aca="false">H115/G115-1</f>
-        <v>0.0349591001338936</v>
+        <v>0.0349591001338931</v>
       </c>
       <c r="I116" s="26" t="n">
         <f aca="false">I115/H115-1</f>
@@ -48334,7 +48334,7 @@
       </c>
       <c r="J116" s="26" t="n">
         <f aca="false">J115/I115-1</f>
-        <v>0.0536605685402629</v>
+        <v>0.0536605685402631</v>
       </c>
     </row>
     <row r="117" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -48358,7 +48358,7 @@
       </c>
       <c r="F117" s="17" t="n">
         <f aca="false">F113/F98</f>
-        <v>0.0556838565999821</v>
+        <v>0.055683856599982</v>
       </c>
       <c r="G117" s="17" t="n">
         <f aca="false">G113/G98</f>
@@ -48431,7 +48431,7 @@
       </c>
       <c r="D123" s="30" t="n">
         <f aca="false">itc_26</f>
-        <v>781.872916666667</v>
+        <v>781.872916666666</v>
       </c>
       <c r="E123" s="30" t="n">
         <f aca="false">itc_27*1</f>
@@ -48530,7 +48530,7 @@
       </c>
       <c r="D127" s="22" t="n">
         <f aca="false">D125*D126</f>
-        <v>634.616531285011</v>
+        <v>634.61653128501</v>
       </c>
       <c r="E127" s="22" t="n">
         <f aca="false">E125*E126</f>
@@ -48554,7 +48554,7 @@
       </c>
       <c r="D128" s="22" t="n">
         <f aca="false">D127*fx</f>
-        <v>20307.7290011204</v>
+        <v>20307.7290011203</v>
       </c>
       <c r="E128" s="22" t="n">
         <f aca="false">E127*fx</f>
@@ -48648,7 +48648,7 @@
       </c>
       <c r="E132" s="17" t="n">
         <f aca="false">$D$129*E130*E131</f>
-        <v>0.0424007886050184</v>
+        <v>0.0424007886050185</v>
       </c>
       <c r="F132" s="17" t="n">
         <f aca="false">$D$129*F130*F131</f>
@@ -48656,7 +48656,7 @@
       </c>
       <c r="G132" s="17" t="n">
         <f aca="false">$D$129*G130*G131</f>
-        <v>0.0359948615198459</v>
+        <v>0.035994861519846</v>
       </c>
     </row>
     <row r="133" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -48727,7 +48727,7 @@
       </c>
       <c r="E135" s="22" t="n">
         <f aca="false">E133*(1-E134)</f>
-        <v>1468.25675675679</v>
+        <v>1468.2567567568</v>
       </c>
       <c r="F135" s="22" t="n">
         <f aca="false">F133*(1-F134)</f>
@@ -48788,7 +48788,7 @@
       </c>
       <c r="E138" s="22" t="n">
         <f aca="false">E135+E137</f>
-        <v>2264.68863299679</v>
+        <v>2264.6886329968</v>
       </c>
       <c r="F138" s="22" t="n">
         <f aca="false">F135+F137</f>
@@ -48804,11 +48804,11 @@
       </c>
       <c r="I138" s="25" t="n">
         <f aca="false">H138*(1+I139)</f>
-        <v>2654.5841631075</v>
+        <v>2654.58416310751</v>
       </c>
       <c r="J138" s="25" t="n">
         <f aca="false">I138*(1+J139)</f>
-        <v>2813.85921289395</v>
+        <v>2813.85921289396</v>
       </c>
       <c r="K138" s="8" t="s">
         <v>457</v>
@@ -48827,23 +48827,23 @@
       </c>
       <c r="E139" s="18" t="n">
         <f aca="false">E138/D138-1</f>
-        <v>0.552574715434458</v>
+        <v>0.552574715434459</v>
       </c>
       <c r="F139" s="18" t="n">
         <f aca="false">F138/E138-1</f>
-        <v>0.0633363643322467</v>
+        <v>0.0633363643322462</v>
       </c>
       <c r="G139" s="18" t="n">
         <f aca="false">G138/F138-1</f>
-        <v>0.0196072127703828</v>
+        <v>0.019607212770383</v>
       </c>
       <c r="H139" s="26" t="n">
         <f aca="false">$G139+(fade_gA-$G139)*1/3</f>
-        <v>0.0330714751802552</v>
+        <v>0.0330714751802554</v>
       </c>
       <c r="I139" s="26" t="n">
         <f aca="false">$G139+(fade_gA-$G139)*2/3</f>
-        <v>0.0465357375901276</v>
+        <v>0.0465357375901277</v>
       </c>
       <c r="J139" s="26" t="n">
         <f aca="false">$G139+(fade_gA-$G139)*3/3</f>
@@ -48867,15 +48867,15 @@
       </c>
       <c r="E140" s="18" t="n">
         <f aca="false">E135/E138</f>
-        <v>0.648326103361014</v>
+        <v>0.648326103361015</v>
       </c>
       <c r="F140" s="18" t="n">
         <f aca="false">F135/F138</f>
-        <v>0.659351334452269</v>
+        <v>0.65935133445227</v>
       </c>
       <c r="G140" s="18" t="n">
         <f aca="false">G135/G138</f>
-        <v>0.655879125687218</v>
+        <v>0.655879125687219</v>
       </c>
     </row>
     <row r="141" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -48887,7 +48887,7 @@
       </c>
       <c r="D141" s="23" t="n">
         <f aca="false">D135/fx/D125</f>
-        <v>0.935061049524468</v>
+        <v>0.935061049524469</v>
       </c>
       <c r="E141" s="23" t="n">
         <f aca="false">E135/fx/E125</f>
@@ -48895,11 +48895,11 @@
       </c>
       <c r="F141" s="23" t="n">
         <f aca="false">F135/fx/F125</f>
-        <v>0.939889559807722</v>
+        <v>0.939889559807723</v>
       </c>
       <c r="G141" s="23" t="n">
         <f aca="false">G135/fx/G125</f>
-        <v>0.83682113881491</v>
+        <v>0.836821138814911</v>
       </c>
     </row>
     <row r="142" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -49113,7 +49113,7 @@
       </c>
       <c r="G150" s="22" t="n">
         <f aca="false">G145-G149</f>
-        <v>182.105505880901</v>
+        <v>182.105505880902</v>
       </c>
     </row>
     <row r="151" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -49273,7 +49273,7 @@
       </c>
       <c r="F155" s="30" t="n">
         <f aca="false">F153/F154</f>
-        <v>237.980894740677</v>
+        <v>237.980894740678</v>
       </c>
       <c r="G155" s="30" t="n">
         <f aca="false">G153/G154</f>
@@ -49289,7 +49289,7 @@
       </c>
       <c r="J155" s="28" t="n">
         <f aca="false">J153/J154</f>
-        <v>285.908346656586</v>
+        <v>285.908346656587</v>
       </c>
     </row>
     <row r="156" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -49305,7 +49305,7 @@
       </c>
       <c r="E156" s="18" t="n">
         <f aca="false">E155/D155-1</f>
-        <v>0.561474228011207</v>
+        <v>0.561474228011208</v>
       </c>
       <c r="F156" s="18" t="n">
         <f aca="false">F155/E155-1</f>
@@ -49313,7 +49313,7 @@
       </c>
       <c r="G156" s="18" t="n">
         <f aca="false">G155/F155-1</f>
-        <v>0.057450793464223</v>
+        <v>0.0574507934642232</v>
       </c>
       <c r="H156" s="26" t="n">
         <f aca="false">H155/G155-1</f>
@@ -49321,7 +49321,7 @@
       </c>
       <c r="I156" s="26" t="n">
         <f aca="false">I155/H155-1</f>
-        <v>0.0435152951282818</v>
+        <v>0.0435152951282813</v>
       </c>
       <c r="J156" s="26" t="n">
         <f aca="false">J155/I155-1</f>
@@ -49422,7 +49422,7 @@
       </c>
       <c r="D163" s="30" t="n">
         <f aca="false">itc_26</f>
-        <v>781.872916666667</v>
+        <v>781.872916666666</v>
       </c>
       <c r="E163" s="30" t="n">
         <f aca="false">itc_27*1</f>
@@ -49521,7 +49521,7 @@
       </c>
       <c r="D167" s="22" t="n">
         <f aca="false">D165*D166</f>
-        <v>634.616531285011</v>
+        <v>634.61653128501</v>
       </c>
       <c r="E167" s="22" t="n">
         <f aca="false">E165*E166</f>
@@ -49545,7 +49545,7 @@
       </c>
       <c r="D168" s="22" t="n">
         <f aca="false">D167*fx</f>
-        <v>20307.7290011204</v>
+        <v>20307.7290011203</v>
       </c>
       <c r="E168" s="22" t="n">
         <f aca="false">E167*fx</f>
@@ -49639,11 +49639,11 @@
       </c>
       <c r="E172" s="17" t="n">
         <f aca="false">$D$169*E170*E171</f>
-        <v>0.054871608782965</v>
+        <v>0.0548716087829651</v>
       </c>
       <c r="F172" s="17" t="n">
         <f aca="false">$D$169*F170*F171</f>
-        <v>0.0560005804263907</v>
+        <v>0.0560005804263908</v>
       </c>
       <c r="G172" s="17" t="n">
         <f aca="false">$D$169*G170*G171</f>
@@ -49722,7 +49722,7 @@
       </c>
       <c r="F175" s="22" t="n">
         <f aca="false">F173*(1-F174)</f>
-        <v>2328.77471908132</v>
+        <v>2328.77471908133</v>
       </c>
       <c r="G175" s="22" t="n">
         <f aca="false">G173*(1-G174)</f>
@@ -49783,11 +49783,11 @@
       </c>
       <c r="F178" s="22" t="n">
         <f aca="false">F175+F177</f>
-        <v>3149.09955160852</v>
+        <v>3149.09955160853</v>
       </c>
       <c r="G178" s="22" t="n">
         <f aca="false">G175+G177</f>
-        <v>3375.575460048</v>
+        <v>3375.57546004801</v>
       </c>
       <c r="H178" s="25" t="n">
         <f aca="false">G178*(1+H179)</f>
@@ -49795,11 +49795,11 @@
       </c>
       <c r="I178" s="25" t="n">
         <f aca="false">H178*(1+I179)</f>
-        <v>3835.54586922699</v>
+        <v>3835.545869227</v>
       </c>
       <c r="J178" s="25" t="n">
         <f aca="false">I178*(1+J179)</f>
-        <v>4065.67862138061</v>
+        <v>4065.67862138062</v>
       </c>
       <c r="K178" s="8" t="s">
         <v>457</v>
@@ -49818,11 +49818,11 @@
       </c>
       <c r="E179" s="18" t="n">
         <f aca="false">E178/D178-1</f>
-        <v>0.848626102326946</v>
+        <v>0.848626102326947</v>
       </c>
       <c r="F179" s="18" t="n">
         <f aca="false">F178/E178-1</f>
-        <v>0.167834545920387</v>
+        <v>0.167834545920388</v>
       </c>
       <c r="G179" s="18" t="n">
         <f aca="false">G178/F178-1</f>
@@ -49878,7 +49878,7 @@
       </c>
       <c r="D181" s="23" t="n">
         <f aca="false">D175/fx/D165</f>
-        <v>0.935061049524468</v>
+        <v>0.935061049524469</v>
       </c>
       <c r="E181" s="23" t="n">
         <f aca="false">E175/fx/E165</f>
@@ -49890,7 +49890,7 @@
       </c>
       <c r="G181" s="23" t="n">
         <f aca="false">G175/fx/G165</f>
-        <v>1.31500464670914</v>
+        <v>1.31500464670915</v>
       </c>
     </row>
     <row r="182" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -49930,7 +49930,7 @@
       </c>
       <c r="F184" s="30" t="n">
         <f aca="false">($D$183+d_ai+vrd)*F173*(1-F174*(1-keep))</f>
-        <v>195.228872503334</v>
+        <v>195.228872503335</v>
       </c>
       <c r="G184" s="30" t="n">
         <f aca="false">($D$183+d_ai+vrd)*G173*(1-G174*(1-keep))</f>
@@ -50104,7 +50104,7 @@
       </c>
       <c r="G190" s="22" t="n">
         <f aca="false">G185-G189</f>
-        <v>252.68109809166</v>
+        <v>252.681098091661</v>
       </c>
     </row>
     <row r="191" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -50192,7 +50192,7 @@
       </c>
       <c r="H193" s="25" t="n">
         <f aca="false">H178*H197</f>
-        <v>210.27592745604</v>
+        <v>210.275927456041</v>
       </c>
       <c r="I193" s="25" t="n">
         <f aca="false">I178*I197</f>
@@ -50272,7 +50272,7 @@
       </c>
       <c r="H195" s="28" t="n">
         <f aca="false">H193/H194</f>
-        <v>370.687615304359</v>
+        <v>370.68761530436</v>
       </c>
       <c r="I195" s="28" t="n">
         <f aca="false">I193/I194</f>
@@ -50296,15 +50296,15 @@
       </c>
       <c r="E196" s="18" t="n">
         <f aca="false">E195/D195-1</f>
-        <v>0.855037573728316</v>
+        <v>0.855037573728317</v>
       </c>
       <c r="F196" s="18" t="n">
         <f aca="false">F195/E195-1</f>
-        <v>0.214386884615632</v>
+        <v>0.214386884615633</v>
       </c>
       <c r="G196" s="18" t="n">
         <f aca="false">G195/F195-1</f>
-        <v>0.118885618341437</v>
+        <v>0.118885618341436</v>
       </c>
       <c r="H196" s="26" t="n">
         <f aca="false">H195/G195-1</f>
@@ -50312,11 +50312,11 @@
       </c>
       <c r="I196" s="26" t="n">
         <f aca="false">I195/H195-1</f>
-        <v>0.057638400170652</v>
+        <v>0.0576384001706516</v>
       </c>
       <c r="J196" s="26" t="n">
         <f aca="false">J195/I195-1</f>
-        <v>0.0536884723899107</v>
+        <v>0.0536884723899109</v>
       </c>
     </row>
     <row r="197" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -50413,7 +50413,7 @@
       </c>
       <c r="D203" s="30" t="n">
         <f aca="false">itc_26</f>
-        <v>781.872916666667</v>
+        <v>781.872916666666</v>
       </c>
       <c r="E203" s="30" t="n">
         <f aca="false">itc_27*1</f>
@@ -50512,7 +50512,7 @@
       </c>
       <c r="D207" s="22" t="n">
         <f aca="false">D205*D206</f>
-        <v>634.616531285011</v>
+        <v>634.61653128501</v>
       </c>
       <c r="E207" s="22" t="n">
         <f aca="false">E205*E206</f>
@@ -50536,7 +50536,7 @@
       </c>
       <c r="D208" s="22" t="n">
         <f aca="false">D207*fx</f>
-        <v>20307.7290011204</v>
+        <v>20307.7290011203</v>
       </c>
       <c r="E208" s="22" t="n">
         <f aca="false">E207*fx</f>
@@ -50638,7 +50638,7 @@
       </c>
       <c r="G212" s="17" t="n">
         <f aca="false">$D$209*G210*G211</f>
-        <v>0.0327536326983339</v>
+        <v>0.032753632698334</v>
       </c>
     </row>
     <row r="213" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -50717,7 +50717,7 @@
       </c>
       <c r="G215" s="22" t="n">
         <f aca="false">G213*(1-G214)</f>
-        <v>1465.39546128362</v>
+        <v>1465.39546128363</v>
       </c>
     </row>
     <row r="216" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -50809,7 +50809,7 @@
       </c>
       <c r="E219" s="18" t="n">
         <f aca="false">E218/D218-1</f>
-        <v>0.36447977478588</v>
+        <v>0.364479774785881</v>
       </c>
       <c r="F219" s="18" t="n">
         <f aca="false">F218/E218-1</f>
@@ -50857,7 +50857,7 @@
       </c>
       <c r="G220" s="18" t="n">
         <f aca="false">G215/G218</f>
-        <v>0.634279707523187</v>
+        <v>0.634279707523188</v>
       </c>
     </row>
     <row r="221" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -50869,19 +50869,19 @@
       </c>
       <c r="D221" s="23" t="n">
         <f aca="false">D215/fx/D205</f>
-        <v>0.935061049524468</v>
+        <v>0.935061049524469</v>
       </c>
       <c r="E221" s="23" t="n">
         <f aca="false">E215/fx/E205</f>
-        <v>0.895844607932131</v>
+        <v>0.895844607932132</v>
       </c>
       <c r="F221" s="23" t="n">
         <f aca="false">F215/fx/F205</f>
-        <v>0.848694891725177</v>
+        <v>0.848694891725178</v>
       </c>
       <c r="G221" s="23" t="n">
         <f aca="false">G215/fx/G205</f>
-        <v>0.761467916742311</v>
+        <v>0.761467916742312</v>
       </c>
     </row>
     <row r="222" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -50917,7 +50917,7 @@
       </c>
       <c r="E224" s="30" t="n">
         <f aca="false">($D$223+d_ai+vrd)*E213*(1-E214*(1-keep))</f>
-        <v>95.2987714404463</v>
+        <v>95.2987714404465</v>
       </c>
       <c r="F224" s="30" t="n">
         <f aca="false">($D$223+d_ai+vrd)*F213*(1-F214*(1-keep))</f>
@@ -51287,7 +51287,7 @@
       </c>
       <c r="E236" s="18" t="n">
         <f aca="false">E235/D235-1</f>
-        <v>0.374960053330748</v>
+        <v>0.374960053330749</v>
       </c>
       <c r="F236" s="18" t="n">
         <f aca="false">F235/E235-1</f>
@@ -51295,7 +51295,7 @@
       </c>
       <c r="G236" s="18" t="n">
         <f aca="false">G235/F235-1</f>
-        <v>0.0617257154737165</v>
+        <v>0.0617257154737163</v>
       </c>
       <c r="H236" s="26" t="n">
         <f aca="false">H235/G235-1</f>
@@ -51307,7 +51307,7 @@
       </c>
       <c r="J236" s="26" t="n">
         <f aca="false">J235/I235-1</f>
-        <v>0.057362995785516</v>
+        <v>0.0573629957855155</v>
       </c>
     </row>
     <row r="237" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -51404,7 +51404,7 @@
       </c>
       <c r="D243" s="30" t="n">
         <f aca="false">itc_26</f>
-        <v>781.872916666667</v>
+        <v>781.872916666666</v>
       </c>
       <c r="E243" s="30" t="n">
         <f aca="false">itc_27*1</f>
@@ -51503,7 +51503,7 @@
       </c>
       <c r="D247" s="22" t="n">
         <f aca="false">D245*D246</f>
-        <v>634.616531285011</v>
+        <v>634.61653128501</v>
       </c>
       <c r="E247" s="22" t="n">
         <f aca="false">E245*E246</f>
@@ -51527,7 +51527,7 @@
       </c>
       <c r="D248" s="22" t="n">
         <f aca="false">D247*fx</f>
-        <v>20307.7290011204</v>
+        <v>20307.7290011203</v>
       </c>
       <c r="E248" s="22" t="n">
         <f aca="false">E247*fx</f>
@@ -51621,7 +51621,7 @@
       </c>
       <c r="E252" s="17" t="n">
         <f aca="false">$D$249*E250*E251</f>
-        <v>0.049027404455771</v>
+        <v>0.0490274044557711</v>
       </c>
       <c r="F252" s="17" t="n">
         <f aca="false">$D$249*F250*F251</f>
@@ -51629,7 +51629,7 @@
       </c>
       <c r="G252" s="17" t="n">
         <f aca="false">$D$249*G250*G251</f>
-        <v>0.047955917177329</v>
+        <v>0.0479559171773291</v>
       </c>
     </row>
     <row r="253" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -51649,7 +51649,7 @@
       </c>
       <c r="F253" s="22" t="n">
         <f aca="false">F248*F252</f>
-        <v>2310.11704479233</v>
+        <v>2310.11704479234</v>
       </c>
       <c r="G253" s="22" t="n">
         <f aca="false">G248*G252</f>
@@ -51700,7 +51700,7 @@
       </c>
       <c r="E255" s="22" t="n">
         <f aca="false">E253*(1-E254)</f>
-        <v>1697.72356191304</v>
+        <v>1697.72356191305</v>
       </c>
       <c r="F255" s="22" t="n">
         <f aca="false">F253*(1-F254)</f>
@@ -51761,7 +51761,7 @@
       </c>
       <c r="E258" s="22" t="n">
         <f aca="false">E255+E257</f>
-        <v>2494.15543815304</v>
+        <v>2494.15543815305</v>
       </c>
       <c r="F258" s="22" t="n">
         <f aca="false">F255+F257</f>
@@ -51777,7 +51777,7 @@
       </c>
       <c r="I258" s="25" t="n">
         <f aca="false">H258*(1+I259)</f>
-        <v>3269.99430278528</v>
+        <v>3269.99430278529</v>
       </c>
       <c r="J258" s="25" t="n">
         <f aca="false">I258*(1+J259)</f>
@@ -51800,11 +51800,11 @@
       </c>
       <c r="E259" s="18" t="n">
         <f aca="false">E258/D258-1</f>
-        <v>0.709887449081946</v>
+        <v>0.709887449081948</v>
       </c>
       <c r="F259" s="18" t="n">
         <f aca="false">F258/E258-1</f>
-        <v>0.162489766470757</v>
+        <v>0.162489766470758</v>
       </c>
       <c r="G259" s="18" t="n">
         <f aca="false">G258/F258-1</f>
@@ -51840,11 +51840,11 @@
       </c>
       <c r="E260" s="18" t="n">
         <f aca="false">E255/E258</f>
-        <v>0.680680737031462</v>
+        <v>0.680680737031463</v>
       </c>
       <c r="F260" s="18" t="n">
         <f aca="false">F255/F258</f>
-        <v>0.717073775319236</v>
+        <v>0.717073775319237</v>
       </c>
       <c r="G260" s="18" t="n">
         <f aca="false">G255/G258</f>
@@ -51860,7 +51860,7 @@
       </c>
       <c r="D261" s="23" t="n">
         <f aca="false">D255/fx/D245</f>
-        <v>0.935061049524468</v>
+        <v>0.935061049524469</v>
       </c>
       <c r="E261" s="23" t="n">
         <f aca="false">E255/fx/E245</f>
@@ -51943,11 +51943,11 @@
       </c>
       <c r="F265" s="22" t="n">
         <f aca="false">$D$263*F257+F264</f>
-        <v>246.660833880416</v>
+        <v>246.660833880417</v>
       </c>
       <c r="G265" s="22" t="n">
         <f aca="false">$D$263*G257+G264</f>
-        <v>264.02015742917</v>
+        <v>264.020157429171</v>
       </c>
     </row>
     <row r="266" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -51975,7 +51975,7 @@
       </c>
       <c r="G266" s="17" t="n">
         <f aca="false">G265/G258</f>
-        <v>0.0882869038823586</v>
+        <v>0.0882869038823585</v>
       </c>
     </row>
     <row r="267" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -52078,7 +52078,7 @@
       </c>
       <c r="E270" s="22" t="n">
         <f aca="false">E265-E269</f>
-        <v>170.464139149947</v>
+        <v>170.464139149948</v>
       </c>
       <c r="F270" s="22" t="n">
         <f aca="false">F265-F269</f>
@@ -52166,7 +52166,7 @@
       </c>
       <c r="F273" s="22" t="n">
         <f aca="false">F270*F272</f>
-        <v>161.276343391105</v>
+        <v>161.276343391106</v>
       </c>
       <c r="G273" s="22" t="n">
         <f aca="false">G270*G272</f>
@@ -52174,7 +52174,7 @@
       </c>
       <c r="H273" s="25" t="n">
         <f aca="false">H258*H277</f>
-        <v>181.178790408329</v>
+        <v>181.17879040833</v>
       </c>
       <c r="I273" s="25" t="n">
         <f aca="false">I258*I277</f>
@@ -52254,7 +52254,7 @@
       </c>
       <c r="H275" s="28" t="n">
         <f aca="false">H273/H274</f>
-        <v>319.393354116734</v>
+        <v>319.393354116735</v>
       </c>
       <c r="I275" s="28" t="n">
         <f aca="false">I273/I274</f>
@@ -52278,7 +52278,7 @@
       </c>
       <c r="E276" s="18" t="n">
         <f aca="false">E275/D275-1</f>
-        <v>0.717464891990876</v>
+        <v>0.717464891990878</v>
       </c>
       <c r="F276" s="18" t="n">
         <f aca="false">F275/E275-1</f>
@@ -52286,19 +52286,19 @@
       </c>
       <c r="G276" s="18" t="n">
         <f aca="false">G275/F275-1</f>
-        <v>0.0737408536737922</v>
+        <v>0.0737408536737925</v>
       </c>
       <c r="H276" s="26" t="n">
         <f aca="false">H275/G275-1</f>
-        <v>0.0358695973639651</v>
+        <v>0.0358695973639649</v>
       </c>
       <c r="I276" s="26" t="n">
         <f aca="false">I275/H275-1</f>
-        <v>0.0453557258352439</v>
+        <v>0.0453557258352437</v>
       </c>
       <c r="J276" s="26" t="n">
         <f aca="false">J275/I275-1</f>
-        <v>0.0548418540817868</v>
+        <v>0.0548418540817865</v>
       </c>
     </row>
     <row r="277" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -52395,7 +52395,7 @@
       </c>
       <c r="D283" s="30" t="n">
         <f aca="false">itc_26</f>
-        <v>781.872916666667</v>
+        <v>781.872916666666</v>
       </c>
       <c r="E283" s="30" t="n">
         <f aca="false">itc_27*1</f>
@@ -52494,7 +52494,7 @@
       </c>
       <c r="D287" s="22" t="n">
         <f aca="false">D285*D286</f>
-        <v>634.616531285011</v>
+        <v>634.61653128501</v>
       </c>
       <c r="E287" s="22" t="n">
         <f aca="false">E285*E286</f>
@@ -52518,7 +52518,7 @@
       </c>
       <c r="D288" s="22" t="n">
         <f aca="false">D287*fx</f>
-        <v>20307.7290011204</v>
+        <v>20307.7290011203</v>
       </c>
       <c r="E288" s="22" t="n">
         <f aca="false">E287*fx</f>
@@ -52612,15 +52612,15 @@
       </c>
       <c r="E292" s="17" t="n">
         <f aca="false">$D$289*E290*E291</f>
-        <v>0.0498832807117864</v>
+        <v>0.0498832807117865</v>
       </c>
       <c r="F292" s="17" t="n">
         <f aca="false">$D$289*F290*F291</f>
-        <v>0.0509096185694461</v>
+        <v>0.0509096185694462</v>
       </c>
       <c r="G292" s="17" t="n">
         <f aca="false">$D$289*G290*G291</f>
-        <v>0.0488501692055052</v>
+        <v>0.0488501692055053</v>
       </c>
     </row>
     <row r="293" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -52752,7 +52752,7 @@
       </c>
       <c r="E298" s="22" t="n">
         <f aca="false">E295+E297</f>
-        <v>2614.70649761064</v>
+        <v>2614.70649761065</v>
       </c>
       <c r="F298" s="22" t="n">
         <f aca="false">F295+F297</f>
@@ -52791,7 +52791,7 @@
       </c>
       <c r="E299" s="18" t="n">
         <f aca="false">E298/D298-1</f>
-        <v>0.79253215533679</v>
+        <v>0.792532155336792</v>
       </c>
       <c r="F299" s="18" t="n">
         <f aca="false">F298/E298-1</f>
@@ -52799,15 +52799,15 @@
       </c>
       <c r="G299" s="18" t="n">
         <f aca="false">G298/F298-1</f>
-        <v>0.0767666011692831</v>
+        <v>0.0767666011692829</v>
       </c>
       <c r="H299" s="26" t="n">
         <f aca="false">$G299+(fade_gA-$G299)*1/3</f>
-        <v>0.0711777341128554</v>
+        <v>0.0711777341128553</v>
       </c>
       <c r="I299" s="26" t="n">
         <f aca="false">$G299+(fade_gA-$G299)*2/3</f>
-        <v>0.0655888670564277</v>
+        <v>0.0655888670564276</v>
       </c>
       <c r="J299" s="26" t="n">
         <f aca="false">$G299+(fade_gA-$G299)*3/3</f>
@@ -52835,11 +52835,11 @@
       </c>
       <c r="F300" s="18" t="n">
         <f aca="false">F295/F298</f>
-        <v>0.741436358993132</v>
+        <v>0.741436358993133</v>
       </c>
       <c r="G300" s="18" t="n">
         <f aca="false">G295/G298</f>
-        <v>0.752666408906191</v>
+        <v>0.752666408906192</v>
       </c>
     </row>
     <row r="301" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -52851,7 +52851,7 @@
       </c>
       <c r="D301" s="23" t="n">
         <f aca="false">D295/fx/D285</f>
-        <v>0.935061049524468</v>
+        <v>0.935061049524469</v>
       </c>
       <c r="E301" s="23" t="n">
         <f aca="false">E295/fx/E285</f>
@@ -53021,7 +53021,7 @@
       </c>
       <c r="G308" s="22" t="n">
         <f aca="false">F308*(1+MAX(0,phi*G299))</f>
-        <v>45.7220271478442</v>
+        <v>45.7220271478443</v>
       </c>
     </row>
     <row r="309" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -53049,7 +53049,7 @@
       </c>
       <c r="G309" s="22" t="n">
         <f aca="false">G308+0*G298</f>
-        <v>45.7220271478442</v>
+        <v>45.7220271478443</v>
       </c>
     </row>
     <row r="310" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -53077,7 +53077,7 @@
       </c>
       <c r="G310" s="22" t="n">
         <f aca="false">G305-G309</f>
-        <v>224.770953265069</v>
+        <v>224.77095326507</v>
       </c>
     </row>
     <row r="311" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -53245,7 +53245,7 @@
       </c>
       <c r="H315" s="28" t="n">
         <f aca="false">H313/H314</f>
-        <v>345.891351062768</v>
+        <v>345.891351062769</v>
       </c>
       <c r="I315" s="28" t="n">
         <f aca="false">I313/I314</f>
@@ -53253,7 +53253,7 @@
       </c>
       <c r="J315" s="28" t="n">
         <f aca="false">J313/J314</f>
-        <v>419.973150523217</v>
+        <v>419.973150523218</v>
       </c>
     </row>
     <row r="316" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -53269,15 +53269,15 @@
       </c>
       <c r="E316" s="18" t="n">
         <f aca="false">E315/D315-1</f>
-        <v>0.733280692362975</v>
+        <v>0.733280692362976</v>
       </c>
       <c r="F316" s="18" t="n">
         <f aca="false">F315/E315-1</f>
-        <v>0.206285048591521</v>
+        <v>0.206285048591522</v>
       </c>
       <c r="G316" s="18" t="n">
         <f aca="false">G315/F315-1</f>
-        <v>0.0723685240173217</v>
+        <v>0.0723685240173213</v>
       </c>
       <c r="H316" s="26" t="n">
         <f aca="false">H315/G315-1</f>
@@ -53285,7 +53285,7 @@
       </c>
       <c r="I316" s="26" t="n">
         <f aca="false">I315/H315-1</f>
-        <v>0.105732103623507</v>
+        <v>0.105732103623506</v>
       </c>
       <c r="J316" s="26" t="n">
         <f aca="false">J315/I315-1</f>
@@ -53386,7 +53386,7 @@
       </c>
       <c r="D323" s="30" t="n">
         <f aca="false">itc_26</f>
-        <v>781.872916666667</v>
+        <v>781.872916666666</v>
       </c>
       <c r="E323" s="30" t="n">
         <f aca="false">itc_27*1</f>
@@ -53485,7 +53485,7 @@
       </c>
       <c r="D327" s="22" t="n">
         <f aca="false">D325*D326</f>
-        <v>634.616531285011</v>
+        <v>634.61653128501</v>
       </c>
       <c r="E327" s="22" t="n">
         <f aca="false">E325*E326</f>
@@ -53509,7 +53509,7 @@
       </c>
       <c r="D328" s="22" t="n">
         <f aca="false">D327*fx</f>
-        <v>20307.7290011204</v>
+        <v>20307.7290011203</v>
       </c>
       <c r="E328" s="22" t="n">
         <f aca="false">E327*fx</f>
@@ -53603,15 +53603,15 @@
       </c>
       <c r="E332" s="17" t="n">
         <f aca="false">$D$329*E330*E331</f>
-        <v>0.0498832807117864</v>
+        <v>0.0498832807117865</v>
       </c>
       <c r="F332" s="17" t="n">
         <f aca="false">$D$329*F330*F331</f>
-        <v>0.0509096185694461</v>
+        <v>0.0509096185694462</v>
       </c>
       <c r="G332" s="17" t="n">
         <f aca="false">$D$329*G330*G331</f>
-        <v>0.0488501692055052</v>
+        <v>0.0488501692055053</v>
       </c>
     </row>
     <row r="333" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -53782,7 +53782,7 @@
       </c>
       <c r="E339" s="18" t="n">
         <f aca="false">E338/D338-1</f>
-        <v>0.605552332036271</v>
+        <v>0.605552332036273</v>
       </c>
       <c r="F339" s="18" t="n">
         <f aca="false">F338/E338-1</f>
@@ -53790,15 +53790,15 @@
       </c>
       <c r="G339" s="18" t="n">
         <f aca="false">G338/F338-1</f>
-        <v>-0.0264293465228186</v>
+        <v>-0.0264293465228189</v>
       </c>
       <c r="H339" s="26" t="n">
         <f aca="false">$G339+(fade_gA-$G339)*1/3</f>
-        <v>0.00238043565145428</v>
+        <v>0.00238043565145405</v>
       </c>
       <c r="I339" s="26" t="n">
         <f aca="false">$G339+(fade_gA-$G339)*2/3</f>
-        <v>0.0311902178257271</v>
+        <v>0.031190217825727</v>
       </c>
       <c r="J339" s="26" t="n">
         <f aca="false">$G339+(fade_gA-$G339)*3/3</f>
@@ -53826,11 +53826,11 @@
       </c>
       <c r="F340" s="18" t="n">
         <f aca="false">F335/F338</f>
-        <v>0.682604153863358</v>
+        <v>0.682604153863359</v>
       </c>
       <c r="G340" s="18" t="n">
         <f aca="false">G335/G338</f>
-        <v>0.664207502195008</v>
+        <v>0.664207502195009</v>
       </c>
     </row>
     <row r="341" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -53842,7 +53842,7 @@
       </c>
       <c r="D341" s="23" t="n">
         <f aca="false">D335/fx/D325</f>
-        <v>0.935061049524468</v>
+        <v>0.935061049524469</v>
       </c>
       <c r="E341" s="23" t="n">
         <f aca="false">E335/fx/E325</f>
@@ -53854,7 +53854,7 @@
       </c>
       <c r="G341" s="23" t="n">
         <f aca="false">G335/fx/G325</f>
-        <v>0.868465635660852</v>
+        <v>0.868465635660853</v>
       </c>
     </row>
     <row r="342" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -53894,7 +53894,7 @@
       </c>
       <c r="F344" s="30" t="n">
         <f aca="false">($D$343+d_ai+vrd)*F333*(1-F334*(1-keep))</f>
-        <v>174.791690257806</v>
+        <v>174.791690257807</v>
       </c>
       <c r="G344" s="30" t="n">
         <f aca="false">($D$343+d_ai+vrd)*G333*(1-G334*(1-keep))</f>
@@ -53925,7 +53925,7 @@
       </c>
       <c r="F345" s="22" t="n">
         <f aca="false">$D$343*F337+F344</f>
-        <v>247.154259871118</v>
+        <v>247.154259871119</v>
       </c>
       <c r="G345" s="22" t="n">
         <f aca="false">$D$343*G337+G344</f>
@@ -54008,11 +54008,11 @@
       </c>
       <c r="F348" s="22" t="n">
         <f aca="false">E348*(1+MAX(0,phi*F339))</f>
-        <v>36.1970765792576</v>
+        <v>36.1970765792577</v>
       </c>
       <c r="G348" s="22" t="n">
         <f aca="false">F348*(1+MAX(0,phi*G339))</f>
-        <v>36.1970765792576</v>
+        <v>36.1970765792577</v>
       </c>
     </row>
     <row r="349" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -54036,11 +54036,11 @@
       </c>
       <c r="F349" s="22" t="n">
         <f aca="false">F348+0*F338</f>
-        <v>36.1970765792576</v>
+        <v>36.1970765792577</v>
       </c>
       <c r="G349" s="22" t="n">
         <f aca="false">G348+0*G338</f>
-        <v>36.1970765792576</v>
+        <v>36.1970765792577</v>
       </c>
     </row>
     <row r="350" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -54148,7 +54148,7 @@
       </c>
       <c r="F353" s="22" t="n">
         <f aca="false">F350*F352</f>
-        <v>164.546602967651</v>
+        <v>164.546602967652</v>
       </c>
       <c r="G353" s="22" t="n">
         <f aca="false">G350*G352</f>
@@ -54224,7 +54224,7 @@
       </c>
       <c r="E355" s="30" t="n">
         <f aca="false">E353/E354</f>
-        <v>241.91855813528</v>
+        <v>241.918558135281</v>
       </c>
       <c r="F355" s="30" t="n">
         <f aca="false">F353/F354</f>
@@ -54260,7 +54260,7 @@
       </c>
       <c r="E356" s="18" t="n">
         <f aca="false">E355/D355-1</f>
-        <v>0.746275321598467</v>
+        <v>0.746275321598469</v>
       </c>
       <c r="F356" s="18" t="n">
         <f aca="false">F355/E355-1</f>
@@ -54268,19 +54268,19 @@
       </c>
       <c r="G356" s="18" t="n">
         <f aca="false">G355/F355-1</f>
-        <v>0.0727569816130858</v>
+        <v>0.0727569816130853</v>
       </c>
       <c r="H356" s="26" t="n">
         <f aca="false">H355/G355-1</f>
-        <v>-0.0605477905234346</v>
+        <v>-0.0605477905234347</v>
       </c>
       <c r="I356" s="26" t="n">
         <f aca="false">I355/H355-1</f>
-        <v>-0.0372229211704089</v>
+        <v>-0.037222921170409</v>
       </c>
       <c r="J356" s="26" t="n">
         <f aca="false">J355/I355-1</f>
-        <v>-0.0146002504735738</v>
+        <v>-0.0146002504735741</v>
       </c>
     </row>
     <row r="357" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -54377,7 +54377,7 @@
       </c>
       <c r="D363" s="30" t="n">
         <f aca="false">itc_26</f>
-        <v>781.872916666667</v>
+        <v>781.872916666666</v>
       </c>
       <c r="E363" s="30" t="n">
         <f aca="false">itc_27*1</f>
@@ -54476,7 +54476,7 @@
       </c>
       <c r="D367" s="22" t="n">
         <f aca="false">D365*D366</f>
-        <v>634.616531285011</v>
+        <v>634.61653128501</v>
       </c>
       <c r="E367" s="22" t="n">
         <f aca="false">E365*E366</f>
@@ -54500,7 +54500,7 @@
       </c>
       <c r="D368" s="22" t="n">
         <f aca="false">D367*fx</f>
-        <v>20307.7290011204</v>
+        <v>20307.7290011203</v>
       </c>
       <c r="E368" s="22" t="n">
         <f aca="false">E367*fx</f>
@@ -54594,15 +54594,15 @@
       </c>
       <c r="E372" s="17" t="n">
         <f aca="false">$D$369*E370*E371</f>
-        <v>0.0498832807117864</v>
+        <v>0.0498832807117865</v>
       </c>
       <c r="F372" s="17" t="n">
         <f aca="false">$D$369*F370*F371</f>
-        <v>0.0509096185694461</v>
+        <v>0.0509096185694462</v>
       </c>
       <c r="G372" s="17" t="n">
         <f aca="false">$D$369*G370*G371</f>
-        <v>0.0488501692055052</v>
+        <v>0.0488501692055053</v>
       </c>
     </row>
     <row r="373" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -54754,7 +54754,7 @@
       </c>
       <c r="J378" s="25" t="n">
         <f aca="false">I378*(1+J379)</f>
-        <v>3513.54543594395</v>
+        <v>3513.54543594396</v>
       </c>
       <c r="K378" s="8" t="s">
         <v>457</v>
@@ -54773,7 +54773,7 @@
       </c>
       <c r="E379" s="18" t="n">
         <f aca="false">E378/D378-1</f>
-        <v>0.730205547569951</v>
+        <v>0.730205547569952</v>
       </c>
       <c r="F379" s="18" t="n">
         <f aca="false">F378/E378-1</f>
@@ -54781,15 +54781,15 @@
       </c>
       <c r="G379" s="18" t="n">
         <f aca="false">G378/F378-1</f>
-        <v>0.0316931767891091</v>
+        <v>0.0316931767891089</v>
       </c>
       <c r="H379" s="26" t="n">
         <f aca="false">$G379+(fade_gA-$G379)*1/3</f>
-        <v>0.0411287845260727</v>
+        <v>0.0411287845260726</v>
       </c>
       <c r="I379" s="26" t="n">
         <f aca="false">$G379+(fade_gA-$G379)*2/3</f>
-        <v>0.0505643922630364</v>
+        <v>0.0505643922630363</v>
       </c>
       <c r="J379" s="26" t="n">
         <f aca="false">$G379+(fade_gA-$G379)*3/3</f>
@@ -54817,7 +54817,7 @@
       </c>
       <c r="F380" s="18" t="n">
         <f aca="false">F375/F378</f>
-        <v>0.720730287080741</v>
+        <v>0.720730287080742</v>
       </c>
       <c r="G380" s="18" t="n">
         <f aca="false">G375/G378</f>
@@ -54833,7 +54833,7 @@
       </c>
       <c r="D381" s="23" t="n">
         <f aca="false">D375/fx/D365</f>
-        <v>0.935061049524468</v>
+        <v>0.935061049524469</v>
       </c>
       <c r="E381" s="23" t="n">
         <f aca="false">E375/fx/E365</f>
@@ -54968,7 +54968,7 @@
       </c>
       <c r="F387" s="17" t="n">
         <f aca="false">F384/F375</f>
-        <v>0.0821396991772842</v>
+        <v>0.0821396991772841</v>
       </c>
       <c r="G387" s="17" t="n">
         <f aca="false">G384/G375</f>
@@ -54995,11 +54995,11 @@
       </c>
       <c r="E388" s="22" t="n">
         <f aca="false">D388*(1+MAX(0,phi*E379))</f>
-        <v>35.6727317290002</v>
+        <v>35.6727317290003</v>
       </c>
       <c r="F388" s="22" t="n">
         <f aca="false">E388*(1+MAX(0,phi*F379))</f>
-        <v>40.3495789783962</v>
+        <v>40.3495789783963</v>
       </c>
       <c r="G388" s="22" t="n">
         <f aca="false">F388*(1+MAX(0,phi*G379))</f>
@@ -55023,11 +55023,11 @@
       </c>
       <c r="E389" s="22" t="n">
         <f aca="false">E388+0*E378</f>
-        <v>35.6727317290002</v>
+        <v>35.6727317290003</v>
       </c>
       <c r="F389" s="22" t="n">
         <f aca="false">F388+0*F378</f>
-        <v>40.3495789783962</v>
+        <v>40.3495789783963</v>
       </c>
       <c r="G389" s="22" t="n">
         <f aca="false">G388+0*G378</f>
@@ -55051,11 +55051,11 @@
       </c>
       <c r="E390" s="22" t="n">
         <f aca="false">E385-E389</f>
-        <v>171.078085296066</v>
+        <v>171.078085296067</v>
       </c>
       <c r="F390" s="22" t="n">
         <f aca="false">F385-F389</f>
-        <v>205.908313250374</v>
+        <v>205.908313250375</v>
       </c>
       <c r="G390" s="22" t="n">
         <f aca="false">G385-G389</f>
@@ -55219,7 +55219,7 @@
       </c>
       <c r="F395" s="30" t="n">
         <f aca="false">F393/F394</f>
-        <v>285.969111792068</v>
+        <v>285.969111792069</v>
       </c>
       <c r="G395" s="30" t="n">
         <f aca="false">G393/G394</f>
@@ -55251,7 +55251,7 @@
       </c>
       <c r="E396" s="18" t="n">
         <f aca="false">E395/D395-1</f>
-        <v>0.723650538759695</v>
+        <v>0.723650538759697</v>
       </c>
       <c r="F396" s="18" t="n">
         <f aca="false">F395/E395-1</f>
@@ -55263,7 +55263,7 @@
       </c>
       <c r="H396" s="26" t="n">
         <f aca="false">H395/G395-1</f>
-        <v>0.04516384115942</v>
+        <v>0.0451638411594195</v>
       </c>
       <c r="I396" s="26" t="n">
         <f aca="false">I395/H395-1</f>
@@ -55271,7 +55271,7 @@
       </c>
       <c r="J396" s="26" t="n">
         <f aca="false">J395/I395-1</f>
-        <v>0.0639442089530016</v>
+        <v>0.0639442089530014</v>
       </c>
     </row>
     <row r="397" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -55368,7 +55368,7 @@
       </c>
       <c r="D403" s="30" t="n">
         <f aca="false">itc_26</f>
-        <v>781.872916666667</v>
+        <v>781.872916666666</v>
       </c>
       <c r="E403" s="30" t="n">
         <f aca="false">itc_27*1</f>
@@ -55467,7 +55467,7 @@
       </c>
       <c r="D407" s="22" t="n">
         <f aca="false">D405*D406</f>
-        <v>634.616531285011</v>
+        <v>634.61653128501</v>
       </c>
       <c r="E407" s="22" t="n">
         <f aca="false">E405*E406</f>
@@ -55491,7 +55491,7 @@
       </c>
       <c r="D408" s="22" t="n">
         <f aca="false">D407*fx</f>
-        <v>20307.7290011204</v>
+        <v>20307.7290011203</v>
       </c>
       <c r="E408" s="22" t="n">
         <f aca="false">E407*fx</f>
@@ -55585,15 +55585,15 @@
       </c>
       <c r="E412" s="17" t="n">
         <f aca="false">$D$409*E410*E411</f>
-        <v>0.0498832807117864</v>
+        <v>0.0498832807117865</v>
       </c>
       <c r="F412" s="17" t="n">
         <f aca="false">$D$409*F410*F411</f>
-        <v>0.0509096185694461</v>
+        <v>0.0509096185694462</v>
       </c>
       <c r="G412" s="17" t="n">
         <f aca="false">$D$409*G410*G411</f>
-        <v>0.0488501692055052</v>
+        <v>0.0488501692055053</v>
       </c>
     </row>
     <row r="413" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -55741,7 +55741,7 @@
       </c>
       <c r="I418" s="25" t="n">
         <f aca="false">H418*(1+I419)</f>
-        <v>2955.865534481</v>
+        <v>2955.86553448101</v>
       </c>
       <c r="J418" s="25" t="n">
         <f aca="false">I418*(1+J419)</f>
@@ -55764,11 +55764,11 @@
       </c>
       <c r="E419" s="18" t="n">
         <f aca="false">E418/D418-1</f>
-        <v>0.730205547569951</v>
+        <v>0.730205547569952</v>
       </c>
       <c r="F419" s="18" t="n">
         <f aca="false">F418/E418-1</f>
-        <v>0.0380537596946233</v>
+        <v>0.0380537596946235</v>
       </c>
       <c r="G419" s="18" t="n">
         <f aca="false">G418/F418-1</f>
@@ -55812,7 +55812,7 @@
       </c>
       <c r="G420" s="18" t="n">
         <f aca="false">G415/G418</f>
-        <v>0.687368693419264</v>
+        <v>0.687368693419265</v>
       </c>
     </row>
     <row r="421" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -55824,7 +55824,7 @@
       </c>
       <c r="D421" s="23" t="n">
         <f aca="false">D415/fx/D405</f>
-        <v>0.935061049524468</v>
+        <v>0.935061049524469</v>
       </c>
       <c r="E421" s="23" t="n">
         <f aca="false">E415/fx/E405</f>
@@ -55832,11 +55832,11 @@
       </c>
       <c r="F421" s="23" t="n">
         <f aca="false">F415/fx/F405</f>
-        <v>1.06520816778208</v>
+        <v>1.06520816778209</v>
       </c>
       <c r="G421" s="23" t="n">
         <f aca="false">G415/fx/G405</f>
-        <v>0.965332956561486</v>
+        <v>0.965332956561487</v>
       </c>
     </row>
     <row r="422" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -55911,7 +55911,7 @@
       </c>
       <c r="G425" s="22" t="n">
         <f aca="false">$D$423*G417+G424</f>
-        <v>238.600566301415</v>
+        <v>238.600566301416</v>
       </c>
     </row>
     <row r="426" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -55986,7 +55986,7 @@
       </c>
       <c r="E428" s="22" t="n">
         <f aca="false">D428*(1+MAX(0,phi*E419))</f>
-        <v>35.6727317290002</v>
+        <v>35.6727317290003</v>
       </c>
       <c r="F428" s="22" t="n">
         <f aca="false">E428*(1+MAX(0,phi*F419))</f>
@@ -55994,7 +55994,7 @@
       </c>
       <c r="G428" s="22" t="n">
         <f aca="false">F428*(1+MAX(0,phi*G419))</f>
-        <v>37.6883787887953</v>
+        <v>37.6883787887954</v>
       </c>
     </row>
     <row r="429" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -56014,7 +56014,7 @@
       </c>
       <c r="E429" s="22" t="n">
         <f aca="false">E428+0*E418</f>
-        <v>35.6727317290002</v>
+        <v>35.6727317290003</v>
       </c>
       <c r="F429" s="22" t="n">
         <f aca="false">F428+0*F418</f>
@@ -56022,7 +56022,7 @@
       </c>
       <c r="G429" s="22" t="n">
         <f aca="false">G428+0*G418</f>
-        <v>37.6883787887953</v>
+        <v>37.6883787887954</v>
       </c>
     </row>
     <row r="430" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -56242,11 +56242,11 @@
       </c>
       <c r="E436" s="18" t="n">
         <f aca="false">E435/D435-1</f>
-        <v>0.737612235441472</v>
+        <v>0.737612235441474</v>
       </c>
       <c r="F436" s="18" t="n">
         <f aca="false">F435/E435-1</f>
-        <v>0.0757899330198466</v>
+        <v>0.0757899330198462</v>
       </c>
       <c r="G436" s="18" t="n">
         <f aca="false">G435/F435-1</f>
@@ -56258,7 +56258,7 @@
       </c>
       <c r="I436" s="26" t="n">
         <f aca="false">I435/H435-1</f>
-        <v>0.0466984748524935</v>
+        <v>0.046698474852493</v>
       </c>
       <c r="J436" s="26" t="n">
         <f aca="false">J435/I435-1</f>
@@ -56282,7 +56282,7 @@
       </c>
       <c r="E437" s="17" t="n">
         <f aca="false">E433/E418</f>
-        <v>0.0533014396086032</v>
+        <v>0.0533014396086033</v>
       </c>
       <c r="F437" s="17" t="n">
         <f aca="false">F433/F418</f>
@@ -56359,7 +56359,7 @@
       </c>
       <c r="D443" s="30" t="n">
         <f aca="false">itc_26</f>
-        <v>781.872916666667</v>
+        <v>781.872916666666</v>
       </c>
       <c r="E443" s="30" t="n">
         <f aca="false">itc_27*1</f>
@@ -56458,7 +56458,7 @@
       </c>
       <c r="D447" s="22" t="n">
         <f aca="false">D445*D446</f>
-        <v>634.616531285011</v>
+        <v>634.61653128501</v>
       </c>
       <c r="E447" s="22" t="n">
         <f aca="false">E445*E446</f>
@@ -56482,7 +56482,7 @@
       </c>
       <c r="D448" s="22" t="n">
         <f aca="false">D447*fx</f>
-        <v>20307.7290011204</v>
+        <v>20307.7290011203</v>
       </c>
       <c r="E448" s="22" t="n">
         <f aca="false">E447*fx</f>
@@ -56576,15 +56576,15 @@
       </c>
       <c r="E452" s="17" t="n">
         <f aca="false">$D$449*E450*E451</f>
-        <v>0.0498832807117864</v>
+        <v>0.0498832807117865</v>
       </c>
       <c r="F452" s="17" t="n">
         <f aca="false">$D$449*F450*F451</f>
-        <v>0.0509096185694461</v>
+        <v>0.0509096185694462</v>
       </c>
       <c r="G452" s="17" t="n">
         <f aca="false">$D$449*G450*G451</f>
-        <v>0.0488501692055052</v>
+        <v>0.0488501692055053</v>
       </c>
     </row>
     <row r="453" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -56608,7 +56608,7 @@
       </c>
       <c r="G453" s="22" t="n">
         <f aca="false">G448*G452</f>
-        <v>3085.48727925271</v>
+        <v>3085.48727925272</v>
       </c>
     </row>
     <row r="454" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -56663,7 +56663,7 @@
       </c>
       <c r="G455" s="22" t="n">
         <f aca="false">G453*(1-G454)</f>
-        <v>2622.6641873648</v>
+        <v>2622.66418736481</v>
       </c>
     </row>
     <row r="456" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -56755,7 +56755,7 @@
       </c>
       <c r="E459" s="18" t="n">
         <f aca="false">E458/D458-1</f>
-        <v>0.730205547569951</v>
+        <v>0.730205547569952</v>
       </c>
       <c r="F459" s="18" t="n">
         <f aca="false">F458/E458-1</f>
@@ -56763,11 +56763,11 @@
       </c>
       <c r="G459" s="18" t="n">
         <f aca="false">G458/F458-1</f>
-        <v>0.0317758328438587</v>
+        <v>0.0317758328438584</v>
       </c>
       <c r="H459" s="26" t="n">
         <f aca="false">$G459+(fade_gA-$G459)*1/3</f>
-        <v>0.0411838885625724</v>
+        <v>0.0411838885625723</v>
       </c>
       <c r="I459" s="26" t="n">
         <f aca="false">$G459+(fade_gA-$G459)*2/3</f>
@@ -56815,7 +56815,7 @@
       </c>
       <c r="D461" s="23" t="n">
         <f aca="false">D455/fx/D445</f>
-        <v>0.935061049524468</v>
+        <v>0.935061049524469</v>
       </c>
       <c r="E461" s="23" t="n">
         <f aca="false">E455/fx/E445</f>
@@ -56823,7 +56823,7 @@
       </c>
       <c r="F461" s="23" t="n">
         <f aca="false">F455/fx/F445</f>
-        <v>1.50382329569235</v>
+        <v>1.50382329569236</v>
       </c>
       <c r="G461" s="23" t="n">
         <f aca="false">G455/fx/G445</f>
@@ -56867,7 +56867,7 @@
       </c>
       <c r="F464" s="30" t="n">
         <f aca="false">($D$463+d_ai+vrd)*F453*(1-F454*(1-keep))</f>
-        <v>212.976951821819</v>
+        <v>212.97695182182</v>
       </c>
       <c r="G464" s="30" t="n">
         <f aca="false">($D$463+d_ai+vrd)*G453*(1-G454*(1-keep))</f>
@@ -56902,7 +56902,7 @@
       </c>
       <c r="G465" s="22" t="n">
         <f aca="false">$D$463*G457+G464</f>
-        <v>306.157615548352</v>
+        <v>306.157615548353</v>
       </c>
     </row>
     <row r="466" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -56977,7 +56977,7 @@
       </c>
       <c r="E468" s="22" t="n">
         <f aca="false">D468*(1+MAX(0,phi*E459))</f>
-        <v>35.6727317290002</v>
+        <v>35.6727317290003</v>
       </c>
       <c r="F468" s="22" t="n">
         <f aca="false">E468*(1+MAX(0,phi*F459))</f>
@@ -56985,7 +56985,7 @@
       </c>
       <c r="G468" s="22" t="n">
         <f aca="false">F468*(1+MAX(0,phi*G459))</f>
-        <v>46.2848176336301</v>
+        <v>46.2848176336302</v>
       </c>
     </row>
     <row r="469" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -57005,7 +57005,7 @@
       </c>
       <c r="E469" s="22" t="n">
         <f aca="false">E468+0*E458</f>
-        <v>35.6727317290002</v>
+        <v>35.6727317290003</v>
       </c>
       <c r="F469" s="22" t="n">
         <f aca="false">F468+0*F458</f>
@@ -57013,7 +57013,7 @@
       </c>
       <c r="G469" s="22" t="n">
         <f aca="false">G468+0*G458</f>
-        <v>46.2848176336301</v>
+        <v>46.2848176336302</v>
       </c>
     </row>
     <row r="470" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -57125,7 +57125,7 @@
       </c>
       <c r="G473" s="22" t="n">
         <f aca="false">G470*G472</f>
-        <v>202.700782373483</v>
+        <v>202.700782373484</v>
       </c>
       <c r="H473" s="25" t="n">
         <f aca="false">H458*H477</f>
@@ -57209,7 +57209,7 @@
       </c>
       <c r="H475" s="28" t="n">
         <f aca="false">H473/H474</f>
-        <v>371.540388544341</v>
+        <v>371.540388544342</v>
       </c>
       <c r="I475" s="28" t="n">
         <f aca="false">I473/I474</f>
@@ -57217,7 +57217,7 @@
       </c>
       <c r="J475" s="28" t="n">
         <f aca="false">J473/J474</f>
-        <v>408.5269203282</v>
+        <v>408.526920328201</v>
       </c>
     </row>
     <row r="476" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -57233,7 +57233,7 @@
       </c>
       <c r="E476" s="18" t="n">
         <f aca="false">E475/D475-1</f>
-        <v>0.737612235441472</v>
+        <v>0.737612235441474</v>
       </c>
       <c r="F476" s="18" t="n">
         <f aca="false">F475/E475-1</f>
@@ -57241,19 +57241,19 @@
       </c>
       <c r="G476" s="18" t="n">
         <f aca="false">G475/F475-1</f>
-        <v>0.0765096139571162</v>
+        <v>0.076509613957116</v>
       </c>
       <c r="H476" s="26" t="n">
         <f aca="false">H475/G475-1</f>
-        <v>0.0345846366002995</v>
+        <v>0.0345846366002998</v>
       </c>
       <c r="I476" s="26" t="n">
         <f aca="false">I475/H475-1</f>
-        <v>0.0439310975166602</v>
+        <v>0.04393109751666</v>
       </c>
       <c r="J476" s="26" t="n">
         <f aca="false">J475/I475-1</f>
-        <v>0.0532775178037088</v>
+        <v>0.0532775178037093</v>
       </c>
     </row>
     <row r="477" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -57273,7 +57273,7 @@
       </c>
       <c r="E477" s="17" t="n">
         <f aca="false">E473/E458</f>
-        <v>0.0533014396086032</v>
+        <v>0.0533014396086033</v>
       </c>
       <c r="F477" s="17" t="n">
         <f aca="false">F473/F458</f>
@@ -57350,7 +57350,7 @@
       </c>
       <c r="D483" s="30" t="n">
         <f aca="false">itc_26</f>
-        <v>781.872916666667</v>
+        <v>781.872916666666</v>
       </c>
       <c r="E483" s="30" t="n">
         <f aca="false">itc_27*1</f>
@@ -57449,7 +57449,7 @@
       </c>
       <c r="D487" s="22" t="n">
         <f aca="false">D485*D486</f>
-        <v>634.616531285011</v>
+        <v>634.61653128501</v>
       </c>
       <c r="E487" s="22" t="n">
         <f aca="false">E485*E486</f>
@@ -57473,7 +57473,7 @@
       </c>
       <c r="D488" s="22" t="n">
         <f aca="false">D487*fx</f>
-        <v>20307.7290011204</v>
+        <v>20307.7290011203</v>
       </c>
       <c r="E488" s="22" t="n">
         <f aca="false">E487*fx</f>
@@ -57567,15 +57567,15 @@
       </c>
       <c r="E492" s="17" t="n">
         <f aca="false">$D$489*E490*E491</f>
-        <v>0.0498832807117864</v>
+        <v>0.0498832807117865</v>
       </c>
       <c r="F492" s="17" t="n">
         <f aca="false">$D$489*F490*F491</f>
-        <v>0.0509096185694461</v>
+        <v>0.0509096185694462</v>
       </c>
       <c r="G492" s="17" t="n">
         <f aca="false">$D$489*G490*G491</f>
-        <v>0.0488501692055052</v>
+        <v>0.0488501692055053</v>
       </c>
     </row>
     <row r="493" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -57719,7 +57719,7 @@
       </c>
       <c r="H498" s="25" t="n">
         <f aca="false">G498*(1+H499)</f>
-        <v>2882.03649035278</v>
+        <v>2882.03649035279</v>
       </c>
       <c r="I498" s="25" t="n">
         <f aca="false">H498*(1+I499)</f>
@@ -57746,7 +57746,7 @@
       </c>
       <c r="E499" s="18" t="n">
         <f aca="false">E498/D498-1</f>
-        <v>0.65220554756995</v>
+        <v>0.652205547569952</v>
       </c>
       <c r="F499" s="18" t="n">
         <f aca="false">F498/E498-1</f>
@@ -57754,15 +57754,15 @@
       </c>
       <c r="G499" s="18" t="n">
         <f aca="false">G498/F498-1</f>
-        <v>0.0130385902099455</v>
+        <v>0.0130385902099448</v>
       </c>
       <c r="H499" s="26" t="n">
         <f aca="false">$G499+(fade_gA-$G499)*1/3</f>
-        <v>0.028692393473297</v>
+        <v>0.0286923934732965</v>
       </c>
       <c r="I499" s="26" t="n">
         <f aca="false">$G499+(fade_gA-$G499)*2/3</f>
-        <v>0.0443461967366485</v>
+        <v>0.0443461967366483</v>
       </c>
       <c r="J499" s="26" t="n">
         <f aca="false">$G499+(fade_gA-$G499)*3/3</f>
@@ -57786,15 +57786,15 @@
       </c>
       <c r="E500" s="18" t="n">
         <f aca="false">E495/E498</f>
-        <v>0.716742265701546</v>
+        <v>0.716742265701547</v>
       </c>
       <c r="F500" s="18" t="n">
         <f aca="false">F495/F498</f>
-        <v>0.765502891350732</v>
+        <v>0.765502891350733</v>
       </c>
       <c r="G500" s="18" t="n">
         <f aca="false">G495/G498</f>
-        <v>0.780094997989527</v>
+        <v>0.780094997989528</v>
       </c>
     </row>
     <row r="501" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -57806,7 +57806,7 @@
       </c>
       <c r="D501" s="23" t="n">
         <f aca="false">D495/fx/D485</f>
-        <v>0.935061049524468</v>
+        <v>0.935061049524469</v>
       </c>
       <c r="E501" s="23" t="n">
         <f aca="false">E495/fx/E485</f>
@@ -57858,7 +57858,7 @@
       </c>
       <c r="F504" s="30" t="n">
         <f aca="false">($D$503+d_ai+vrd)*F493*(1-F494*(1-keep))</f>
-        <v>177.480793184849</v>
+        <v>177.48079318485</v>
       </c>
       <c r="G504" s="30" t="n">
         <f aca="false">($D$503+d_ai+vrd)*G493*(1-G494*(1-keep))</f>
@@ -57921,7 +57921,7 @@
       </c>
       <c r="G506" s="17" t="n">
         <f aca="false">G505/G498</f>
-        <v>0.0882934352079545</v>
+        <v>0.0882934352079546</v>
       </c>
     </row>
     <row r="507" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -57968,7 +57968,7 @@
       </c>
       <c r="E508" s="22" t="n">
         <f aca="false">D508*(1+MAX(0,phi*E499))</f>
-        <v>34.2675881678802</v>
+        <v>34.2675881678803</v>
       </c>
       <c r="F508" s="22" t="n">
         <f aca="false">E508*(1+MAX(0,phi*F499))</f>
@@ -57976,7 +57976,7 @@
       </c>
       <c r="G508" s="22" t="n">
         <f aca="false">F508*(1+MAX(0,phi*G499))</f>
-        <v>38.7118946187382</v>
+        <v>38.7118946187383</v>
       </c>
     </row>
     <row r="509" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -57996,7 +57996,7 @@
       </c>
       <c r="E509" s="22" t="n">
         <f aca="false">E508+0*E498</f>
-        <v>34.2675881678802</v>
+        <v>34.2675881678803</v>
       </c>
       <c r="F509" s="22" t="n">
         <f aca="false">F508+0*F498</f>
@@ -58004,7 +58004,7 @@
       </c>
       <c r="G509" s="22" t="n">
         <f aca="false">G508+0*G498</f>
-        <v>38.7118946187382</v>
+        <v>38.7118946187383</v>
       </c>
     </row>
     <row r="510" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -58192,11 +58192,11 @@
       </c>
       <c r="F515" s="30" t="n">
         <f aca="false">F513/F514</f>
-        <v>272.730616620601</v>
+        <v>272.730616620602</v>
       </c>
       <c r="G515" s="30" t="n">
         <f aca="false">G513/G514</f>
-        <v>288.342665667954</v>
+        <v>288.342665667955</v>
       </c>
       <c r="H515" s="28" t="n">
         <f aca="false">H513/H514</f>
@@ -58224,7 +58224,7 @@
       </c>
       <c r="E516" s="18" t="n">
         <f aca="false">E515/D515-1</f>
-        <v>0.650650192261557</v>
+        <v>0.650650192261559</v>
       </c>
       <c r="F516" s="18" t="n">
         <f aca="false">F515/E515-1</f>
@@ -58236,15 +58236,15 @@
       </c>
       <c r="H516" s="26" t="n">
         <f aca="false">H515/G515-1</f>
-        <v>0.0243041160082167</v>
+        <v>0.024304116008216</v>
       </c>
       <c r="I516" s="26" t="n">
         <f aca="false">I515/H515-1</f>
-        <v>0.0398906144513387</v>
+        <v>0.0398906144513385</v>
       </c>
       <c r="J516" s="26" t="n">
         <f aca="false">J515/I515-1</f>
-        <v>0.0554770978406716</v>
+        <v>0.0554770978406711</v>
       </c>
     </row>
     <row r="517" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -58341,7 +58341,7 @@
       </c>
       <c r="D523" s="30" t="n">
         <f aca="false">itc_26</f>
-        <v>781.872916666667</v>
+        <v>781.872916666666</v>
       </c>
       <c r="E523" s="30" t="n">
         <f aca="false">itc_27*1</f>
@@ -58440,7 +58440,7 @@
       </c>
       <c r="D527" s="22" t="n">
         <f aca="false">D525*D526</f>
-        <v>634.616531285011</v>
+        <v>634.61653128501</v>
       </c>
       <c r="E527" s="22" t="n">
         <f aca="false">E525*E526</f>
@@ -58464,7 +58464,7 @@
       </c>
       <c r="D528" s="22" t="n">
         <f aca="false">D527*fx</f>
-        <v>20307.7290011204</v>
+        <v>20307.7290011203</v>
       </c>
       <c r="E528" s="22" t="n">
         <f aca="false">E527*fx</f>
@@ -58558,15 +58558,15 @@
       </c>
       <c r="E532" s="17" t="n">
         <f aca="false">$D$529*E530*E531</f>
-        <v>0.0498832807117864</v>
+        <v>0.0498832807117865</v>
       </c>
       <c r="F532" s="17" t="n">
         <f aca="false">$D$529*F530*F531</f>
-        <v>0.0509096185694461</v>
+        <v>0.0509096185694462</v>
       </c>
       <c r="G532" s="17" t="n">
         <f aca="false">$D$529*G530*G531</f>
-        <v>0.0488501692055052</v>
+        <v>0.0488501692055053</v>
       </c>
     </row>
     <row r="533" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -58714,7 +58714,7 @@
       </c>
       <c r="I538" s="25" t="n">
         <f aca="false">H538*(1+I539)</f>
-        <v>3576.48153506729</v>
+        <v>3576.4815350673</v>
       </c>
       <c r="J538" s="25" t="n">
         <f aca="false">I538*(1+J539)</f>
@@ -58737,7 +58737,7 @@
       </c>
       <c r="E539" s="18" t="n">
         <f aca="false">E538/D538-1</f>
-        <v>0.78220554756995</v>
+        <v>0.782205547569952</v>
       </c>
       <c r="F539" s="18" t="n">
         <f aca="false">F538/E538-1</f>
@@ -58745,11 +58745,11 @@
       </c>
       <c r="G539" s="18" t="n">
         <f aca="false">G538/F538-1</f>
-        <v>0.0472103721149566</v>
+        <v>0.0472103721149564</v>
       </c>
       <c r="H539" s="26" t="n">
         <f aca="false">$G539+(fade_gA-$G539)*1/3</f>
-        <v>0.0514735814099711</v>
+        <v>0.0514735814099709</v>
       </c>
       <c r="I539" s="26" t="n">
         <f aca="false">$G539+(fade_gA-$G539)*2/3</f>
@@ -58777,7 +58777,7 @@
       </c>
       <c r="E540" s="18" t="n">
         <f aca="false">E535/E538</f>
-        <v>0.664460701059214</v>
+        <v>0.664460701059215</v>
       </c>
       <c r="F540" s="18" t="n">
         <f aca="false">F535/F538</f>
@@ -58785,7 +58785,7 @@
       </c>
       <c r="G540" s="18" t="n">
         <f aca="false">G535/G538</f>
-        <v>0.678358817413906</v>
+        <v>0.678358817413907</v>
       </c>
     </row>
     <row r="541" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -58797,7 +58797,7 @@
       </c>
       <c r="D541" s="23" t="n">
         <f aca="false">D535/fx/D525</f>
-        <v>0.935061049524468</v>
+        <v>0.935061049524469</v>
       </c>
       <c r="E541" s="23" t="n">
         <f aca="false">E535/fx/E525</f>
@@ -58849,7 +58849,7 @@
       </c>
       <c r="F544" s="30" t="n">
         <f aca="false">($D$543+d_ai+vrd)*F533*(1-F534*(1-keep))</f>
-        <v>177.480793184849</v>
+        <v>177.48079318485</v>
       </c>
       <c r="G544" s="30" t="n">
         <f aca="false">($D$543+d_ai+vrd)*G533*(1-G534*(1-keep))</f>
@@ -58884,7 +58884,7 @@
       </c>
       <c r="G545" s="22" t="n">
         <f aca="false">$D$543*G537+G544</f>
-        <v>284.431830585984</v>
+        <v>284.431830585985</v>
       </c>
     </row>
     <row r="546" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -58959,7 +58959,7 @@
       </c>
       <c r="E548" s="22" t="n">
         <f aca="false">D548*(1+MAX(0,phi*E539))</f>
-        <v>36.6094941030802</v>
+        <v>36.6094941030803</v>
       </c>
       <c r="F548" s="22" t="n">
         <f aca="false">E548*(1+MAX(0,phi*F539))</f>
@@ -58967,7 +58967,7 @@
       </c>
       <c r="G548" s="22" t="n">
         <f aca="false">F548*(1+MAX(0,phi*G539))</f>
-        <v>43.568262563506</v>
+        <v>43.5682625635061</v>
       </c>
     </row>
     <row r="549" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -58987,7 +58987,7 @@
       </c>
       <c r="E549" s="22" t="n">
         <f aca="false">E548+0*E538</f>
-        <v>36.6094941030802</v>
+        <v>36.6094941030803</v>
       </c>
       <c r="F549" s="22" t="n">
         <f aca="false">F548+0*F538</f>
@@ -58995,7 +58995,7 @@
       </c>
       <c r="G549" s="22" t="n">
         <f aca="false">G548+0*G538</f>
-        <v>43.568262563506</v>
+        <v>43.5682625635061</v>
       </c>
     </row>
     <row r="550" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -59023,7 +59023,7 @@
       </c>
       <c r="G550" s="22" t="n">
         <f aca="false">G545-G549</f>
-        <v>240.863568022478</v>
+        <v>240.863568022479</v>
       </c>
     </row>
     <row r="551" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -59179,11 +59179,11 @@
       </c>
       <c r="E555" s="30" t="n">
         <f aca="false">E553/E554</f>
-        <v>248.749894106613</v>
+        <v>248.749894106614</v>
       </c>
       <c r="F555" s="30" t="n">
         <f aca="false">F553/F554</f>
-        <v>305.732382436289</v>
+        <v>305.73238243629</v>
       </c>
       <c r="G555" s="30" t="n">
         <f aca="false">G553/G554</f>
@@ -59215,7 +59215,7 @@
       </c>
       <c r="E556" s="18" t="n">
         <f aca="false">E555/D555-1</f>
-        <v>0.795586930894749</v>
+        <v>0.795586930894751</v>
       </c>
       <c r="F556" s="18" t="n">
         <f aca="false">F555/E555-1</f>
@@ -59223,19 +59223,19 @@
       </c>
       <c r="G556" s="18" t="n">
         <f aca="false">G555/F555-1</f>
-        <v>0.0887015935842119</v>
+        <v>0.0887015935842117</v>
       </c>
       <c r="H556" s="26" t="n">
         <f aca="false">H555/G555-1</f>
-        <v>0.0456601211406265</v>
+        <v>0.0456601211406262</v>
       </c>
       <c r="I556" s="26" t="n">
         <f aca="false">I555/H555-1</f>
-        <v>0.0498994341832959</v>
+        <v>0.0498994341832957</v>
       </c>
       <c r="J556" s="26" t="n">
         <f aca="false">J555/I555-1</f>
-        <v>0.0541387442327563</v>
+        <v>0.0541387442327561</v>
       </c>
     </row>
     <row r="557" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -59332,7 +59332,7 @@
       </c>
       <c r="D563" s="30" t="n">
         <f aca="false">itc_26</f>
-        <v>781.872916666667</v>
+        <v>781.872916666666</v>
       </c>
       <c r="E563" s="30" t="n">
         <f aca="false">itc_27*1</f>
@@ -59431,7 +59431,7 @@
       </c>
       <c r="D567" s="22" t="n">
         <f aca="false">D565*D566</f>
-        <v>634.616531285011</v>
+        <v>634.61653128501</v>
       </c>
       <c r="E567" s="22" t="n">
         <f aca="false">E565*E566</f>
@@ -59455,7 +59455,7 @@
       </c>
       <c r="D568" s="22" t="n">
         <f aca="false">D567*fx</f>
-        <v>20307.7290011204</v>
+        <v>20307.7290011203</v>
       </c>
       <c r="E568" s="22" t="n">
         <f aca="false">E567*fx</f>
@@ -59549,15 +59549,15 @@
       </c>
       <c r="E572" s="17" t="n">
         <f aca="false">$D$569*E570*E571</f>
-        <v>0.0498832807117864</v>
+        <v>0.0498832807117865</v>
       </c>
       <c r="F572" s="17" t="n">
         <f aca="false">$D$569*F570*F571</f>
-        <v>0.0509096185694461</v>
+        <v>0.0509096185694462</v>
       </c>
       <c r="G572" s="17" t="n">
         <f aca="false">$D$569*G570*G571</f>
-        <v>0.0488501692055052</v>
+        <v>0.0488501692055053</v>
       </c>
     </row>
     <row r="573" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -59709,7 +59709,7 @@
       </c>
       <c r="J578" s="25" t="n">
         <f aca="false">I578*(1+J579)</f>
-        <v>3513.54543594395</v>
+        <v>3513.54543594396</v>
       </c>
       <c r="K578" s="8" t="s">
         <v>457</v>
@@ -59728,7 +59728,7 @@
       </c>
       <c r="E579" s="18" t="n">
         <f aca="false">E578/D578-1</f>
-        <v>0.730205547569951</v>
+        <v>0.730205547569952</v>
       </c>
       <c r="F579" s="18" t="n">
         <f aca="false">F578/E578-1</f>
@@ -59736,15 +59736,15 @@
       </c>
       <c r="G579" s="18" t="n">
         <f aca="false">G578/F578-1</f>
-        <v>0.0316931767891091</v>
+        <v>0.0316931767891089</v>
       </c>
       <c r="H579" s="26" t="n">
         <f aca="false">$G579+(fade_gA-$G579)*1/3</f>
-        <v>0.0411287845260727</v>
+        <v>0.0411287845260726</v>
       </c>
       <c r="I579" s="26" t="n">
         <f aca="false">$G579+(fade_gA-$G579)*2/3</f>
-        <v>0.0505643922630364</v>
+        <v>0.0505643922630363</v>
       </c>
       <c r="J579" s="26" t="n">
         <f aca="false">$G579+(fade_gA-$G579)*3/3</f>
@@ -59772,7 +59772,7 @@
       </c>
       <c r="F580" s="18" t="n">
         <f aca="false">F575/F578</f>
-        <v>0.720730287080741</v>
+        <v>0.720730287080742</v>
       </c>
       <c r="G580" s="18" t="n">
         <f aca="false">G575/G578</f>
@@ -59788,7 +59788,7 @@
       </c>
       <c r="D581" s="23" t="n">
         <f aca="false">D575/fx/D565</f>
-        <v>0.935061049524468</v>
+        <v>0.935061049524469</v>
       </c>
       <c r="E581" s="23" t="n">
         <f aca="false">E575/fx/E565</f>
@@ -59895,7 +59895,7 @@
       </c>
       <c r="E586" s="17" t="n">
         <f aca="false">E585/E578</f>
-        <v>0.0802568598154691</v>
+        <v>0.0802568598154692</v>
       </c>
       <c r="F586" s="17" t="n">
         <f aca="false">F585/F578</f>
@@ -59919,7 +59919,7 @@
       </c>
       <c r="E587" s="17" t="n">
         <f aca="false">E584/E575</f>
-        <v>0.0743758226947997</v>
+        <v>0.0743758226947998</v>
       </c>
       <c r="F587" s="17" t="n">
         <f aca="false">F584/F575</f>
@@ -59950,11 +59950,11 @@
       </c>
       <c r="E588" s="22" t="n">
         <f aca="false">D588*(1+MAX(0,phi*E579))</f>
-        <v>35.6727317290002</v>
+        <v>35.6727317290003</v>
       </c>
       <c r="F588" s="22" t="n">
         <f aca="false">E588*(1+MAX(0,phi*F579))</f>
-        <v>40.3495789783962</v>
+        <v>40.3495789783963</v>
       </c>
       <c r="G588" s="22" t="n">
         <f aca="false">F588*(1+MAX(0,phi*G579))</f>
@@ -59978,11 +59978,11 @@
       </c>
       <c r="E589" s="22" t="n">
         <f aca="false">E588+0*E578</f>
-        <v>35.6727317290002</v>
+        <v>35.6727317290003</v>
       </c>
       <c r="F589" s="22" t="n">
         <f aca="false">F588+0*F578</f>
-        <v>40.3495789783962</v>
+        <v>40.3495789783963</v>
       </c>
       <c r="G589" s="22" t="n">
         <f aca="false">G588+0*G578</f>
@@ -60098,11 +60098,11 @@
       </c>
       <c r="G593" s="22" t="n">
         <f aca="false">G590*G592</f>
-        <v>169.312073677742</v>
+        <v>169.312073677743</v>
       </c>
       <c r="H593" s="25" t="n">
         <f aca="false">H578*H597</f>
-        <v>178.742828629436</v>
+        <v>178.742828629437</v>
       </c>
       <c r="I593" s="25" t="n">
         <f aca="false">I578*I597</f>
@@ -60174,7 +60174,7 @@
       </c>
       <c r="F595" s="30" t="n">
         <f aca="false">F593/F594</f>
-        <v>279.599162192864</v>
+        <v>279.599162192865</v>
       </c>
       <c r="G595" s="30" t="n">
         <f aca="false">G593/G594</f>
@@ -60206,7 +60206,7 @@
       </c>
       <c r="E596" s="18" t="n">
         <f aca="false">E595/D595-1</f>
-        <v>0.681343303005953</v>
+        <v>0.681343303005954</v>
       </c>
       <c r="F596" s="18" t="n">
         <f aca="false">F595/E595-1</f>
@@ -60214,19 +60214,19 @@
       </c>
       <c r="G596" s="18" t="n">
         <f aca="false">G595/F595-1</f>
-        <v>0.0728441666206119</v>
+        <v>0.0728441666206117</v>
       </c>
       <c r="H596" s="26" t="n">
         <f aca="false">H595/G595-1</f>
-        <v>0.0504481869605165</v>
+        <v>0.0504481869605162</v>
       </c>
       <c r="I596" s="26" t="n">
         <f aca="false">I595/H595-1</f>
-        <v>0.0597663122935761</v>
+        <v>0.0597663122935759</v>
       </c>
       <c r="J596" s="26" t="n">
         <f aca="false">J595/I595-1</f>
-        <v>0.0690863583912178</v>
+        <v>0.069086358391218</v>
       </c>
     </row>
     <row r="597" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -60323,7 +60323,7 @@
       </c>
       <c r="D603" s="30" t="n">
         <f aca="false">itc_26</f>
-        <v>781.872916666667</v>
+        <v>781.872916666666</v>
       </c>
       <c r="E603" s="30" t="n">
         <f aca="false">itc_27*1</f>
@@ -60422,7 +60422,7 @@
       </c>
       <c r="D607" s="22" t="n">
         <f aca="false">D605*D606</f>
-        <v>634.616531285011</v>
+        <v>634.61653128501</v>
       </c>
       <c r="E607" s="22" t="n">
         <f aca="false">E605*E606</f>
@@ -60446,7 +60446,7 @@
       </c>
       <c r="D608" s="22" t="n">
         <f aca="false">D607*fx</f>
-        <v>20307.7290011204</v>
+        <v>20307.7290011203</v>
       </c>
       <c r="E608" s="22" t="n">
         <f aca="false">E607*fx</f>
@@ -60540,15 +60540,15 @@
       </c>
       <c r="E612" s="17" t="n">
         <f aca="false">$D$609*E610*E611</f>
-        <v>0.0498832807117864</v>
+        <v>0.0498832807117865</v>
       </c>
       <c r="F612" s="17" t="n">
         <f aca="false">$D$609*F610*F611</f>
-        <v>0.0509096185694461</v>
+        <v>0.0509096185694462</v>
       </c>
       <c r="G612" s="17" t="n">
         <f aca="false">$D$609*G610*G611</f>
-        <v>0.0488501692055052</v>
+        <v>0.0488501692055053</v>
       </c>
     </row>
     <row r="613" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -60700,7 +60700,7 @@
       </c>
       <c r="J618" s="25" t="n">
         <f aca="false">I618*(1+J619)</f>
-        <v>3513.54543594395</v>
+        <v>3513.54543594396</v>
       </c>
       <c r="K618" s="8" t="s">
         <v>457</v>
@@ -60719,7 +60719,7 @@
       </c>
       <c r="E619" s="18" t="n">
         <f aca="false">E618/D618-1</f>
-        <v>0.730205547569951</v>
+        <v>0.730205547569952</v>
       </c>
       <c r="F619" s="18" t="n">
         <f aca="false">F618/E618-1</f>
@@ -60727,15 +60727,15 @@
       </c>
       <c r="G619" s="18" t="n">
         <f aca="false">G618/F618-1</f>
-        <v>0.0316931767891091</v>
+        <v>0.0316931767891089</v>
       </c>
       <c r="H619" s="26" t="n">
         <f aca="false">$G619+(fade_gA-$G619)*1/3</f>
-        <v>0.0411287845260727</v>
+        <v>0.0411287845260726</v>
       </c>
       <c r="I619" s="26" t="n">
         <f aca="false">$G619+(fade_gA-$G619)*2/3</f>
-        <v>0.0505643922630364</v>
+        <v>0.0505643922630363</v>
       </c>
       <c r="J619" s="26" t="n">
         <f aca="false">$G619+(fade_gA-$G619)*3/3</f>
@@ -60763,7 +60763,7 @@
       </c>
       <c r="F620" s="18" t="n">
         <f aca="false">F615/F618</f>
-        <v>0.720730287080741</v>
+        <v>0.720730287080742</v>
       </c>
       <c r="G620" s="18" t="n">
         <f aca="false">G615/G618</f>
@@ -60779,7 +60779,7 @@
       </c>
       <c r="D621" s="23" t="n">
         <f aca="false">D615/fx/D605</f>
-        <v>0.935061049524468</v>
+        <v>0.935061049524469</v>
       </c>
       <c r="E621" s="23" t="n">
         <f aca="false">E615/fx/E605</f>
@@ -60831,11 +60831,11 @@
       </c>
       <c r="F624" s="30" t="n">
         <f aca="false">($D$623+d_ai_hi+vrd)*F613*(1-F614*(1-keep))</f>
-        <v>189.590421724072</v>
+        <v>189.590421724073</v>
       </c>
       <c r="G624" s="30" t="n">
         <f aca="false">($D$623+d_ai_hi+vrd)*G613*(1-G614*(1-keep))</f>
-        <v>206.190028909144</v>
+        <v>206.190028909145</v>
       </c>
       <c r="K624" s="4" t="s">
         <v>464</v>
@@ -60866,7 +60866,7 @@
       </c>
       <c r="G625" s="22" t="n">
         <f aca="false">$D$623*G617+G624</f>
-        <v>276.667789638841</v>
+        <v>276.667789638842</v>
       </c>
     </row>
     <row r="626" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -60941,11 +60941,11 @@
       </c>
       <c r="E628" s="22" t="n">
         <f aca="false">D628*(1+MAX(0,phi*E619))</f>
-        <v>35.6727317290002</v>
+        <v>35.6727317290003</v>
       </c>
       <c r="F628" s="22" t="n">
         <f aca="false">E628*(1+MAX(0,phi*F619))</f>
-        <v>40.3495789783962</v>
+        <v>40.3495789783963</v>
       </c>
       <c r="G628" s="22" t="n">
         <f aca="false">F628*(1+MAX(0,phi*G619))</f>
@@ -60969,11 +60969,11 @@
       </c>
       <c r="E629" s="22" t="n">
         <f aca="false">E628+0*E618</f>
-        <v>35.6727317290002</v>
+        <v>35.6727317290003</v>
       </c>
       <c r="F629" s="22" t="n">
         <f aca="false">F628+0*F618</f>
-        <v>40.3495789783962</v>
+        <v>40.3495789783963</v>
       </c>
       <c r="G629" s="22" t="n">
         <f aca="false">G628+0*G618</f>
@@ -60997,7 +60997,7 @@
       </c>
       <c r="E630" s="22" t="n">
         <f aca="false">E625-E629</f>
-        <v>178.048710308704</v>
+        <v>178.048710308705</v>
       </c>
       <c r="F630" s="22" t="n">
         <f aca="false">F625-F629</f>
@@ -61005,7 +61005,7 @@
       </c>
       <c r="G630" s="22" t="n">
         <f aca="false">G625-G629</f>
-        <v>235.295165588502</v>
+        <v>235.295165588503</v>
       </c>
     </row>
     <row r="631" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -61081,7 +61081,7 @@
       </c>
       <c r="E633" s="22" t="n">
         <f aca="false">E630*E632</f>
-        <v>138.877994040789</v>
+        <v>138.87799404079</v>
       </c>
       <c r="F633" s="22" t="n">
         <f aca="false">F630*F632</f>
@@ -61197,7 +61197,7 @@
       </c>
       <c r="E636" s="18" t="n">
         <f aca="false">E635/D635-1</f>
-        <v>0.793881167876992</v>
+        <v>0.793881167876993</v>
       </c>
       <c r="F636" s="18" t="n">
         <f aca="false">F635/E635-1</f>
@@ -61205,15 +61205,15 @@
       </c>
       <c r="G636" s="18" t="n">
         <f aca="false">G635/F635-1</f>
-        <v>0.075614477292218</v>
+        <v>0.0756144772922178</v>
       </c>
       <c r="H636" s="26" t="n">
         <f aca="false">H635/G635-1</f>
-        <v>0.0225731460870515</v>
+        <v>0.0225731460870513</v>
       </c>
       <c r="I636" s="26" t="n">
         <f aca="false">I635/H635-1</f>
-        <v>0.031664035918187</v>
+        <v>0.0316640359181868</v>
       </c>
       <c r="J636" s="26" t="n">
         <f aca="false">J635/I635-1</f>
@@ -61314,7 +61314,7 @@
       </c>
       <c r="D643" s="30" t="n">
         <f aca="false">itc_26</f>
-        <v>781.872916666667</v>
+        <v>781.872916666666</v>
       </c>
       <c r="E643" s="30" t="n">
         <f aca="false">itc_27*1</f>
@@ -61413,7 +61413,7 @@
       </c>
       <c r="D647" s="22" t="n">
         <f aca="false">D645*D646</f>
-        <v>634.616531285011</v>
+        <v>634.61653128501</v>
       </c>
       <c r="E647" s="22" t="n">
         <f aca="false">E645*E646</f>
@@ -61437,7 +61437,7 @@
       </c>
       <c r="D648" s="22" t="n">
         <f aca="false">D647*fx</f>
-        <v>20307.7290011204</v>
+        <v>20307.7290011203</v>
       </c>
       <c r="E648" s="22" t="n">
         <f aca="false">E647*fx</f>
@@ -61531,15 +61531,15 @@
       </c>
       <c r="E652" s="17" t="n">
         <f aca="false">$D$649*E650*E651</f>
-        <v>0.0498832807117864</v>
+        <v>0.0498832807117865</v>
       </c>
       <c r="F652" s="17" t="n">
         <f aca="false">$D$649*F650*F651</f>
-        <v>0.0509096185694461</v>
+        <v>0.0509096185694462</v>
       </c>
       <c r="G652" s="17" t="n">
         <f aca="false">$D$649*G650*G651</f>
-        <v>0.0488501692055052</v>
+        <v>0.0488501692055053</v>
       </c>
     </row>
     <row r="653" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -61691,7 +61691,7 @@
       </c>
       <c r="J658" s="25" t="n">
         <f aca="false">I658*(1+J659)</f>
-        <v>3513.54543594395</v>
+        <v>3513.54543594396</v>
       </c>
       <c r="K658" s="8" t="s">
         <v>457</v>
@@ -61710,7 +61710,7 @@
       </c>
       <c r="E659" s="18" t="n">
         <f aca="false">E658/D658-1</f>
-        <v>0.730205547569951</v>
+        <v>0.730205547569952</v>
       </c>
       <c r="F659" s="18" t="n">
         <f aca="false">F658/E658-1</f>
@@ -61718,15 +61718,15 @@
       </c>
       <c r="G659" s="18" t="n">
         <f aca="false">G658/F658-1</f>
-        <v>0.0316931767891091</v>
+        <v>0.0316931767891089</v>
       </c>
       <c r="H659" s="26" t="n">
         <f aca="false">$G659+(fade_gA-$G659)*1/3</f>
-        <v>0.0411287845260727</v>
+        <v>0.0411287845260726</v>
       </c>
       <c r="I659" s="26" t="n">
         <f aca="false">$G659+(fade_gA-$G659)*2/3</f>
-        <v>0.0505643922630364</v>
+        <v>0.0505643922630363</v>
       </c>
       <c r="J659" s="26" t="n">
         <f aca="false">$G659+(fade_gA-$G659)*3/3</f>
@@ -61754,7 +61754,7 @@
       </c>
       <c r="F660" s="18" t="n">
         <f aca="false">F655/F658</f>
-        <v>0.720730287080741</v>
+        <v>0.720730287080742</v>
       </c>
       <c r="G660" s="18" t="n">
         <f aca="false">G655/G658</f>
@@ -61770,7 +61770,7 @@
       </c>
       <c r="D661" s="23" t="n">
         <f aca="false">D655/fx/D645</f>
-        <v>0.935061049524468</v>
+        <v>0.935061049524469</v>
       </c>
       <c r="E661" s="23" t="n">
         <f aca="false">E655/fx/E645</f>
@@ -61822,7 +61822,7 @@
       </c>
       <c r="F664" s="30" t="n">
         <f aca="false">($D$663+d_ai+vrd_lo)*F653*(1-F654*(1-keep))</f>
-        <v>170.494469027605</v>
+        <v>170.494469027606</v>
       </c>
       <c r="G664" s="30" t="n">
         <f aca="false">($D$663+d_ai+vrd_lo)*G653*(1-G654*(1-keep))</f>
@@ -61932,11 +61932,11 @@
       </c>
       <c r="E668" s="22" t="n">
         <f aca="false">D668*(1+MAX(0,phi*E659))</f>
-        <v>35.6727317290002</v>
+        <v>35.6727317290003</v>
       </c>
       <c r="F668" s="22" t="n">
         <f aca="false">E668*(1+MAX(0,phi*F659))</f>
-        <v>40.3495789783962</v>
+        <v>40.3495789783963</v>
       </c>
       <c r="G668" s="22" t="n">
         <f aca="false">F668*(1+MAX(0,phi*G659))</f>
@@ -61960,11 +61960,11 @@
       </c>
       <c r="E669" s="22" t="n">
         <f aca="false">E668+0*E658</f>
-        <v>35.6727317290002</v>
+        <v>35.6727317290003</v>
       </c>
       <c r="F669" s="22" t="n">
         <f aca="false">F668+0*F658</f>
-        <v>40.3495789783962</v>
+        <v>40.3495789783963</v>
       </c>
       <c r="G669" s="22" t="n">
         <f aca="false">G668+0*G658</f>
@@ -61992,7 +61992,7 @@
       </c>
       <c r="F670" s="22" t="n">
         <f aca="false">F665-F669</f>
-        <v>202.507459662521</v>
+        <v>202.507459662522</v>
       </c>
       <c r="G670" s="22" t="n">
         <f aca="false">G665-G669</f>
@@ -62156,7 +62156,7 @@
       </c>
       <c r="F675" s="30" t="n">
         <f aca="false">F673/F674</f>
-        <v>281.245946104869</v>
+        <v>281.24594610487</v>
       </c>
       <c r="G675" s="30" t="n">
         <f aca="false">G673/G674</f>
@@ -62188,7 +62188,7 @@
       </c>
       <c r="E676" s="18" t="n">
         <f aca="false">E675/D675-1</f>
-        <v>0.682928439877799</v>
+        <v>0.682928439877801</v>
       </c>
       <c r="F676" s="18" t="n">
         <f aca="false">F675/E675-1</f>
@@ -62196,11 +62196,11 @@
       </c>
       <c r="G676" s="18" t="n">
         <f aca="false">G675/F675-1</f>
-        <v>0.0740121570157633</v>
+        <v>0.0740121570157628</v>
       </c>
       <c r="H676" s="26" t="n">
         <f aca="false">H675/G675-1</f>
-        <v>0.0479523446178838</v>
+        <v>0.0479523446178836</v>
       </c>
       <c r="I676" s="26" t="n">
         <f aca="false">I675/H675-1</f>
@@ -62305,7 +62305,7 @@
       </c>
       <c r="D683" s="30" t="n">
         <f aca="false">itc_26</f>
-        <v>781.872916666667</v>
+        <v>781.872916666666</v>
       </c>
       <c r="E683" s="30" t="n">
         <f aca="false">itc_27*1</f>
@@ -62404,7 +62404,7 @@
       </c>
       <c r="D687" s="22" t="n">
         <f aca="false">D685*D686</f>
-        <v>634.616531285011</v>
+        <v>634.61653128501</v>
       </c>
       <c r="E687" s="22" t="n">
         <f aca="false">E685*E686</f>
@@ -62428,7 +62428,7 @@
       </c>
       <c r="D688" s="22" t="n">
         <f aca="false">D687*fx</f>
-        <v>20307.7290011204</v>
+        <v>20307.7290011203</v>
       </c>
       <c r="E688" s="22" t="n">
         <f aca="false">E687*fx</f>
@@ -62522,15 +62522,15 @@
       </c>
       <c r="E692" s="17" t="n">
         <f aca="false">$D$689*E690*E691</f>
-        <v>0.0498832807117864</v>
+        <v>0.0498832807117865</v>
       </c>
       <c r="F692" s="17" t="n">
         <f aca="false">$D$689*F690*F691</f>
-        <v>0.0509096185694461</v>
+        <v>0.0509096185694462</v>
       </c>
       <c r="G692" s="17" t="n">
         <f aca="false">$D$689*G690*G691</f>
-        <v>0.0488501692055052</v>
+        <v>0.0488501692055053</v>
       </c>
     </row>
     <row r="693" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -62682,7 +62682,7 @@
       </c>
       <c r="J698" s="25" t="n">
         <f aca="false">I698*(1+J699)</f>
-        <v>3513.54543594395</v>
+        <v>3513.54543594396</v>
       </c>
       <c r="K698" s="8" t="s">
         <v>457</v>
@@ -62701,7 +62701,7 @@
       </c>
       <c r="E699" s="18" t="n">
         <f aca="false">E698/D698-1</f>
-        <v>0.730205547569951</v>
+        <v>0.730205547569952</v>
       </c>
       <c r="F699" s="18" t="n">
         <f aca="false">F698/E698-1</f>
@@ -62709,15 +62709,15 @@
       </c>
       <c r="G699" s="18" t="n">
         <f aca="false">G698/F698-1</f>
-        <v>0.0316931767891091</v>
+        <v>0.0316931767891089</v>
       </c>
       <c r="H699" s="26" t="n">
         <f aca="false">$G699+(fade_gA-$G699)*1/3</f>
-        <v>0.0411287845260727</v>
+        <v>0.0411287845260726</v>
       </c>
       <c r="I699" s="26" t="n">
         <f aca="false">$G699+(fade_gA-$G699)*2/3</f>
-        <v>0.0505643922630364</v>
+        <v>0.0505643922630363</v>
       </c>
       <c r="J699" s="26" t="n">
         <f aca="false">$G699+(fade_gA-$G699)*3/3</f>
@@ -62745,7 +62745,7 @@
       </c>
       <c r="F700" s="18" t="n">
         <f aca="false">F695/F698</f>
-        <v>0.720730287080741</v>
+        <v>0.720730287080742</v>
       </c>
       <c r="G700" s="18" t="n">
         <f aca="false">G695/G698</f>
@@ -62761,7 +62761,7 @@
       </c>
       <c r="D701" s="23" t="n">
         <f aca="false">D695/fx/D685</f>
-        <v>0.935061049524468</v>
+        <v>0.935061049524469</v>
       </c>
       <c r="E701" s="23" t="n">
         <f aca="false">E695/fx/E685</f>
@@ -62813,7 +62813,7 @@
       </c>
       <c r="F704" s="30" t="n">
         <f aca="false">($D$703+d_ai+vrd)*F693*(1-F694*(1-keep))</f>
-        <v>177.480793184849</v>
+        <v>177.48079318485</v>
       </c>
       <c r="G704" s="30" t="n">
         <f aca="false">($D$703+d_ai+vrd)*G693*(1-G694*(1-keep))</f>
@@ -62923,11 +62923,11 @@
       </c>
       <c r="E708" s="22" t="n">
         <f aca="false">D708*(1+MAX(0,phi*E699))</f>
-        <v>35.6727317290002</v>
+        <v>35.6727317290003</v>
       </c>
       <c r="F708" s="22" t="n">
         <f aca="false">E708*(1+MAX(0,phi*F699))</f>
-        <v>40.3495789783962</v>
+        <v>40.3495789783963</v>
       </c>
       <c r="G708" s="22" t="n">
         <f aca="false">F708*(1+MAX(0,phi*G699))</f>
@@ -62979,7 +62979,7 @@
       </c>
       <c r="E710" s="22" t="n">
         <f aca="false">E705-E709</f>
-        <v>167.4162448906</v>
+        <v>167.416244890601</v>
       </c>
       <c r="F710" s="22" t="n">
         <f aca="false">F705-F709</f>
@@ -63015,7 +63015,7 @@
       </c>
       <c r="G711" s="17" t="n">
         <f aca="false">G710/G698</f>
-        <v>0.0726351605280453</v>
+        <v>0.0726351605280452</v>
       </c>
     </row>
     <row r="712" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -63151,7 +63151,7 @@
       </c>
       <c r="G715" s="30" t="n">
         <f aca="false">G713/G714</f>
-        <v>304.185608233016</v>
+        <v>304.185608233017</v>
       </c>
       <c r="H715" s="28" t="n">
         <f aca="false">H713/H714</f>
@@ -63179,7 +63179,7 @@
       </c>
       <c r="E716" s="18" t="n">
         <f aca="false">E715/D715-1</f>
-        <v>0.686756665550801</v>
+        <v>0.686756665550803</v>
       </c>
       <c r="F716" s="18" t="n">
         <f aca="false">F715/E715-1</f>
@@ -63187,19 +63187,19 @@
       </c>
       <c r="G716" s="18" t="n">
         <f aca="false">G715/F715-1</f>
-        <v>0.0756602514257754</v>
+        <v>0.0756602514257749</v>
       </c>
       <c r="H716" s="26" t="n">
         <f aca="false">H715/G715-1</f>
-        <v>0.0454572814516363</v>
+        <v>0.0454572814516361</v>
       </c>
       <c r="I716" s="26" t="n">
         <f aca="false">I715/H715-1</f>
-        <v>0.0548448583292214</v>
+        <v>0.0548448583292209</v>
       </c>
       <c r="J716" s="26" t="n">
         <f aca="false">J715/I715-1</f>
-        <v>0.0642324548104192</v>
+        <v>0.0642324548104194</v>
       </c>
     </row>
     <row r="717" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -63296,7 +63296,7 @@
       </c>
       <c r="D723" s="30" t="n">
         <f aca="false">itc_26</f>
-        <v>781.872916666667</v>
+        <v>781.872916666666</v>
       </c>
       <c r="E723" s="30" t="n">
         <f aca="false">itc_27*1</f>
@@ -63395,7 +63395,7 @@
       </c>
       <c r="D727" s="22" t="n">
         <f aca="false">D725*D726</f>
-        <v>634.616531285011</v>
+        <v>634.61653128501</v>
       </c>
       <c r="E727" s="22" t="n">
         <f aca="false">E725*E726</f>
@@ -63419,7 +63419,7 @@
       </c>
       <c r="D728" s="22" t="n">
         <f aca="false">D727*fx</f>
-        <v>20307.7290011204</v>
+        <v>20307.7290011203</v>
       </c>
       <c r="E728" s="22" t="n">
         <f aca="false">E727*fx</f>
@@ -63513,15 +63513,15 @@
       </c>
       <c r="E732" s="17" t="n">
         <f aca="false">$D$729*E730*E731</f>
-        <v>0.0498832807117864</v>
+        <v>0.0498832807117865</v>
       </c>
       <c r="F732" s="17" t="n">
         <f aca="false">$D$729*F730*F731</f>
-        <v>0.0509096185694461</v>
+        <v>0.0509096185694462</v>
       </c>
       <c r="G732" s="17" t="n">
         <f aca="false">$D$729*G730*G731</f>
-        <v>0.0488501692055052</v>
+        <v>0.0488501692055053</v>
       </c>
     </row>
     <row r="733" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -63673,7 +63673,7 @@
       </c>
       <c r="J738" s="25" t="n">
         <f aca="false">I738*(1+J739)</f>
-        <v>3513.54543594395</v>
+        <v>3513.54543594396</v>
       </c>
       <c r="K738" s="8" t="s">
         <v>457</v>
@@ -63692,7 +63692,7 @@
       </c>
       <c r="E739" s="18" t="n">
         <f aca="false">E738/D738-1</f>
-        <v>0.730205547569951</v>
+        <v>0.730205547569952</v>
       </c>
       <c r="F739" s="18" t="n">
         <f aca="false">F738/E738-1</f>
@@ -63700,15 +63700,15 @@
       </c>
       <c r="G739" s="18" t="n">
         <f aca="false">G738/F738-1</f>
-        <v>0.0316931767891091</v>
+        <v>0.0316931767891089</v>
       </c>
       <c r="H739" s="26" t="n">
         <f aca="false">$G739+(fade_gA-$G739)*1/3</f>
-        <v>0.0411287845260727</v>
+        <v>0.0411287845260726</v>
       </c>
       <c r="I739" s="26" t="n">
         <f aca="false">$G739+(fade_gA-$G739)*2/3</f>
-        <v>0.0505643922630364</v>
+        <v>0.0505643922630363</v>
       </c>
       <c r="J739" s="26" t="n">
         <f aca="false">$G739+(fade_gA-$G739)*3/3</f>
@@ -63736,7 +63736,7 @@
       </c>
       <c r="F740" s="18" t="n">
         <f aca="false">F735/F738</f>
-        <v>0.720730287080741</v>
+        <v>0.720730287080742</v>
       </c>
       <c r="G740" s="18" t="n">
         <f aca="false">G735/G738</f>
@@ -63752,7 +63752,7 @@
       </c>
       <c r="D741" s="23" t="n">
         <f aca="false">D735/fx/D725</f>
-        <v>0.935061049524468</v>
+        <v>0.935061049524469</v>
       </c>
       <c r="E741" s="23" t="n">
         <f aca="false">E735/fx/E725</f>
@@ -63804,7 +63804,7 @@
       </c>
       <c r="F744" s="30" t="n">
         <f aca="false">($D$743+d_ai+vrd)*F733*(1-F734*(1-keep))</f>
-        <v>177.480793184849</v>
+        <v>177.48079318485</v>
       </c>
       <c r="G744" s="30" t="n">
         <f aca="false">($D$743+d_ai+vrd)*G733*(1-G734*(1-keep))</f>
@@ -63998,7 +63998,7 @@
       </c>
       <c r="E751" s="17" t="n">
         <f aca="false">E750/E738</f>
-        <v>0.0670321396071771</v>
+        <v>0.0670321396071772</v>
       </c>
       <c r="F751" s="17" t="n">
         <f aca="false">F750/F738</f>
@@ -64134,7 +64134,7 @@
       </c>
       <c r="E755" s="30" t="n">
         <f aca="false">E753/E754</f>
-        <v>236.12832175549</v>
+        <v>236.128321755491</v>
       </c>
       <c r="F755" s="30" t="n">
         <f aca="false">F753/F754</f>
@@ -64150,7 +64150,7 @@
       </c>
       <c r="I755" s="28" t="n">
         <f aca="false">I753/I754</f>
-        <v>335.778730733631</v>
+        <v>335.778730733632</v>
       </c>
       <c r="J755" s="28" t="n">
         <f aca="false">J753/J754</f>
@@ -64170,19 +64170,19 @@
       </c>
       <c r="E756" s="18" t="n">
         <f aca="false">E755/D755-1</f>
-        <v>0.704478830357003</v>
+        <v>0.704478830357005</v>
       </c>
       <c r="F756" s="18" t="n">
         <f aca="false">F755/E755-1</f>
-        <v>0.202774404498218</v>
+        <v>0.202774404498217</v>
       </c>
       <c r="G756" s="18" t="n">
         <f aca="false">G755/F755-1</f>
-        <v>0.0742049723830265</v>
+        <v>0.074204972383026</v>
       </c>
       <c r="H756" s="26" t="n">
         <f aca="false">H755/G755-1</f>
-        <v>0.0444124294060801</v>
+        <v>0.0444124294060799</v>
       </c>
       <c r="I756" s="26" t="n">
         <f aca="false">I755/H755-1</f>
@@ -64287,7 +64287,7 @@
       </c>
       <c r="D763" s="30" t="n">
         <f aca="false">itc_26</f>
-        <v>781.872916666667</v>
+        <v>781.872916666666</v>
       </c>
       <c r="E763" s="30" t="n">
         <f aca="false">itc_27*1</f>
@@ -64386,7 +64386,7 @@
       </c>
       <c r="D767" s="22" t="n">
         <f aca="false">D765*D766</f>
-        <v>634.616531285011</v>
+        <v>634.61653128501</v>
       </c>
       <c r="E767" s="22" t="n">
         <f aca="false">E765*E766</f>
@@ -64410,7 +64410,7 @@
       </c>
       <c r="D768" s="22" t="n">
         <f aca="false">D767*fx</f>
-        <v>20307.7290011204</v>
+        <v>20307.7290011203</v>
       </c>
       <c r="E768" s="22" t="n">
         <f aca="false">E767*fx</f>
@@ -64504,15 +64504,15 @@
       </c>
       <c r="E772" s="17" t="n">
         <f aca="false">$D$769*E770*E771</f>
-        <v>0.0498832807117864</v>
+        <v>0.0498832807117865</v>
       </c>
       <c r="F772" s="17" t="n">
         <f aca="false">$D$769*F770*F771</f>
-        <v>0.0509096185694461</v>
+        <v>0.0509096185694462</v>
       </c>
       <c r="G772" s="17" t="n">
         <f aca="false">$D$769*G770*G771</f>
-        <v>0.0488501692055052</v>
+        <v>0.0488501692055053</v>
       </c>
     </row>
     <row r="773" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -64664,7 +64664,7 @@
       </c>
       <c r="J778" s="25" t="n">
         <f aca="false">I778*(1+J779)</f>
-        <v>3513.54543594395</v>
+        <v>3513.54543594396</v>
       </c>
       <c r="K778" s="8" t="s">
         <v>457</v>
@@ -64683,7 +64683,7 @@
       </c>
       <c r="E779" s="18" t="n">
         <f aca="false">E778/D778-1</f>
-        <v>0.730205547569951</v>
+        <v>0.730205547569952</v>
       </c>
       <c r="F779" s="18" t="n">
         <f aca="false">F778/E778-1</f>
@@ -64691,15 +64691,15 @@
       </c>
       <c r="G779" s="18" t="n">
         <f aca="false">G778/F778-1</f>
-        <v>0.0316931767891091</v>
+        <v>0.0316931767891089</v>
       </c>
       <c r="H779" s="26" t="n">
         <f aca="false">$G779+(fade_gA-$G779)*1/3</f>
-        <v>0.0411287845260727</v>
+        <v>0.0411287845260726</v>
       </c>
       <c r="I779" s="26" t="n">
         <f aca="false">$G779+(fade_gA-$G779)*2/3</f>
-        <v>0.0505643922630364</v>
+        <v>0.0505643922630363</v>
       </c>
       <c r="J779" s="26" t="n">
         <f aca="false">$G779+(fade_gA-$G779)*3/3</f>
@@ -64727,7 +64727,7 @@
       </c>
       <c r="F780" s="18" t="n">
         <f aca="false">F775/F778</f>
-        <v>0.720730287080741</v>
+        <v>0.720730287080742</v>
       </c>
       <c r="G780" s="18" t="n">
         <f aca="false">G775/G778</f>
@@ -64743,7 +64743,7 @@
       </c>
       <c r="D781" s="23" t="n">
         <f aca="false">D775/fx/D765</f>
-        <v>0.935061049524468</v>
+        <v>0.935061049524469</v>
       </c>
       <c r="E781" s="23" t="n">
         <f aca="false">E775/fx/E765</f>
@@ -64795,7 +64795,7 @@
       </c>
       <c r="F784" s="30" t="n">
         <f aca="false">($D$783+d_ai+vrd)*F773*(1-F774*(1-keep))</f>
-        <v>177.480793184849</v>
+        <v>177.48079318485</v>
       </c>
       <c r="G784" s="30" t="n">
         <f aca="false">($D$783+d_ai+vrd)*G773*(1-G774*(1-keep))</f>
@@ -64905,11 +64905,11 @@
       </c>
       <c r="E788" s="22" t="n">
         <f aca="false">D788*(1+MAX(0,phi*E779))</f>
-        <v>35.6727317290002</v>
+        <v>35.6727317290003</v>
       </c>
       <c r="F788" s="22" t="n">
         <f aca="false">E788*(1+MAX(0,phi*F779))</f>
-        <v>40.3495789783962</v>
+        <v>40.3495789783963</v>
       </c>
       <c r="G788" s="22" t="n">
         <f aca="false">F788*(1+MAX(0,phi*G779))</f>
@@ -64933,11 +64933,11 @@
       </c>
       <c r="E789" s="22" t="n">
         <f aca="false">E788+0*E778</f>
-        <v>35.6727317290002</v>
+        <v>35.6727317290003</v>
       </c>
       <c r="F789" s="22" t="n">
         <f aca="false">F788+0*F778</f>
-        <v>40.3495789783962</v>
+        <v>40.3495789783963</v>
       </c>
       <c r="G789" s="22" t="n">
         <f aca="false">G788+0*G778</f>
@@ -64965,7 +64965,7 @@
       </c>
       <c r="F790" s="22" t="n">
         <f aca="false">F785-F789</f>
-        <v>209.493783819765</v>
+        <v>209.493783819766</v>
       </c>
       <c r="G790" s="22" t="n">
         <f aca="false">G785-G789</f>
@@ -64997,7 +64997,7 @@
       </c>
       <c r="G791" s="17" t="n">
         <f aca="false">G790/G778</f>
-        <v>0.0746351605280453</v>
+        <v>0.0746351605280452</v>
       </c>
     </row>
     <row r="792" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -65125,7 +65125,7 @@
       </c>
       <c r="E795" s="30" t="n">
         <f aca="false">E793/E794</f>
-        <v>222.201623904004</v>
+        <v>222.201623904005</v>
       </c>
       <c r="F795" s="30" t="n">
         <f aca="false">F793/F794</f>
@@ -65161,7 +65161,7 @@
       </c>
       <c r="E796" s="18" t="n">
         <f aca="false">E795/D795-1</f>
-        <v>0.603949755792128</v>
+        <v>0.60394975579213</v>
       </c>
       <c r="F796" s="18" t="n">
         <f aca="false">F795/E795-1</f>
@@ -65169,7 +65169,7 @@
       </c>
       <c r="G796" s="18" t="n">
         <f aca="false">G795/F795-1</f>
-        <v>0.07428335499381</v>
+        <v>0.0742833549938093</v>
       </c>
       <c r="H796" s="26" t="n">
         <f aca="false">H795/G795-1</f>

--- a/wiwynn/dist/20261025_緯穎模型_v0.1.1.xlsx
+++ b/wiwynn/dist/20261025_緯穎模型_v0.1.1.xlsx
@@ -5644,26 +5644,26 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">tsmc/dist/20261025_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">台積電模型</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">_v0.3.1.xlsx</t>
+      <t xml:space="preserve">tsmc/dist/20261028_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">台積電個股模型</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">_v0.4.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -5843,26 +5843,26 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">tsmc/dist/20261025_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">台積電模型</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">_v0.3.1.xlsx</t>
+      <t xml:space="preserve">tsmc/dist/20261028_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">台積電個股模型</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">_v0.4.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -5964,26 +5964,26 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">tsmc/dist/20261025_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">台積電模型</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">_v0.3.1.xlsx</t>
+      <t xml:space="preserve">tsmc/dist/20261028_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">台積電個股模型</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">_v0.4.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -6085,26 +6085,26 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">tsmc/dist/20261025_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">台積電模型</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">_v0.3.1.xlsx</t>
+      <t xml:space="preserve">tsmc/dist/20261028_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">台積電個股模型</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">_v0.4.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -6206,26 +6206,26 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">tsmc/dist/20261025_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">台積電模型</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">_v0.3.1.xlsx</t>
+      <t xml:space="preserve">tsmc/dist/20261028_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">台積電個股模型</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">_v0.4.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -6327,26 +6327,26 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">tsmc/dist/20261025_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">台積電模型</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">_v0.3.1.xlsx</t>
+      <t xml:space="preserve">tsmc/dist/20261028_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">台積電個股模型</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">_v0.4.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -6559,26 +6559,26 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">tsmc/dist/20261025_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">台積電模型</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">_v0.3.1.xlsx</t>
+      <t xml:space="preserve">tsmc/dist/20261028_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">台積電個股模型</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">_v0.4.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -34641,26 +34641,26 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">tsmc/dist/20261025_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">台積電模型</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">_v0.3.1.xlsx</t>
+      <t xml:space="preserve">tsmc/dist/20261028_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">台積電個股模型</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">_v0.4.xlsx</t>
     </r>
     <r>
       <rPr>

--- a/wiwynn/dist/20261025_緯穎模型_v0.1.1.xlsx
+++ b/wiwynn/dist/20261025_緯穎模型_v0.1.1.xlsx
@@ -5224,26 +5224,26 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">quanta/dist/20261025_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">廣達模型</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">_v0.2.1.xlsx</t>
+      <t xml:space="preserve">quanta/dist/20261028_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">廣達個股模型</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">_v0.3.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -6413,26 +6413,26 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">quanta/dist/20261025_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">廣達模型</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">_v0.2.1.xlsx</t>
+      <t xml:space="preserve">quanta/dist/20261028_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">廣達個股模型</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">_v0.3.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -7398,26 +7398,26 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">quanta/dist/20261025_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">廣達模型</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">_v0.2.1.xlsx</t>
+      <t xml:space="preserve">quanta/dist/20261028_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">廣達個股模型</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">_v0.3.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -7578,26 +7578,26 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">quanta/dist/20261025_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">廣達模型</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">_v0.2.1.xlsx</t>
+      <t xml:space="preserve">quanta/dist/20261028_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">廣達個股模型</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">_v0.3.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -7680,26 +7680,26 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">quanta/dist/20261025_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">廣達模型</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">_v0.2.1.xlsx</t>
+      <t xml:space="preserve">quanta/dist/20261028_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">廣達個股模型</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">_v0.3.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -7803,26 +7803,26 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">quanta/dist/20261025_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">廣達模型</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">_v0.2.1.xlsx</t>
+      <t xml:space="preserve">quanta/dist/20261028_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">廣達個股模型</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">_v0.3.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -19106,26 +19106,26 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">quanta/dist/20261025_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">廣達模型</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">_v0.2.1.xlsx</t>
+      <t xml:space="preserve">quanta/dist/20261028_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">廣達個股模型</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">_v0.3.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -34679,26 +34679,26 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">quanta/dist/20261025_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">廣達模型</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">_v0.2.1.xlsx</t>
+      <t xml:space="preserve">quanta/dist/20261028_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">廣達個股模型</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">_v0.3.xlsx</t>
     </r>
   </si>
   <si>
